--- a/web/files/港岛-半山区西部-21 Borrett Road 第1期.xlsx
+++ b/web/files/港岛-半山区西部-21 Borrett Road 第1期.xlsx
@@ -636,7 +636,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:N118"/>
+  <dimension ref="A1:N117"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="33" customWidth="1" min="1" max="1"/>
@@ -2224,11 +2224,11 @@
       </c>
       <c r="D25" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>4+房</t>
         </is>
       </c>
       <c r="E25" s="4" t="n">
-        <v>2945</v>
+        <v>2886</v>
       </c>
       <c r="F25" s="3" t="inlineStr">
         <is>
@@ -2240,15 +2240,11 @@
           <t>2024-04-29</t>
         </is>
       </c>
-      <c r="H25" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="I25" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+      <c r="H25" s="5" t="n">
+        <v>218000000</v>
+      </c>
+      <c r="I25" s="5" t="n">
+        <v>75537</v>
       </c>
       <c r="J25" s="3" t="inlineStr">
         <is>
@@ -2284,12 +2280,12 @@
       </c>
       <c r="B26" s="3" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>9</t>
         </is>
       </c>
       <c r="C26" s="3" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="D26" s="3" t="inlineStr">
@@ -2298,23 +2294,27 @@
         </is>
       </c>
       <c r="E26" s="4" t="n">
-        <v>2886</v>
+        <v>2154</v>
       </c>
       <c r="F26" s="3" t="inlineStr">
         <is>
-          <t>已售</t>
+          <t>待售</t>
         </is>
       </c>
       <c r="G26" s="3" t="inlineStr">
         <is>
-          <t>2024-04-29</t>
-        </is>
-      </c>
-      <c r="H26" s="5" t="n">
-        <v>218000000</v>
-      </c>
-      <c r="I26" s="5" t="n">
-        <v>75537</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H26" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="I26" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
       </c>
       <c r="J26" s="3" t="inlineStr">
         <is>
@@ -2355,7 +2355,7 @@
       </c>
       <c r="C27" s="3" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D27" s="3" t="inlineStr">
@@ -2364,7 +2364,7 @@
         </is>
       </c>
       <c r="E27" s="4" t="n">
-        <v>2154</v>
+        <v>2945</v>
       </c>
       <c r="F27" s="3" t="inlineStr">
         <is>
@@ -2420,12 +2420,12 @@
       </c>
       <c r="B28" s="3" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>8</t>
         </is>
       </c>
       <c r="C28" s="3" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="D28" s="3" t="inlineStr">
@@ -2434,7 +2434,7 @@
         </is>
       </c>
       <c r="E28" s="4" t="n">
-        <v>2945</v>
+        <v>2154</v>
       </c>
       <c r="F28" s="3" t="inlineStr">
         <is>
@@ -2495,7 +2495,7 @@
       </c>
       <c r="C29" s="3" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D29" s="3" t="inlineStr">
@@ -2504,7 +2504,7 @@
         </is>
       </c>
       <c r="E29" s="4" t="n">
-        <v>2154</v>
+        <v>2945</v>
       </c>
       <c r="F29" s="3" t="inlineStr">
         <is>
@@ -2560,12 +2560,12 @@
       </c>
       <c r="B30" s="3" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7</t>
         </is>
       </c>
       <c r="C30" s="3" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="D30" s="3" t="inlineStr">
@@ -2574,7 +2574,7 @@
         </is>
       </c>
       <c r="E30" s="4" t="n">
-        <v>2945</v>
+        <v>2154</v>
       </c>
       <c r="F30" s="3" t="inlineStr">
         <is>
@@ -2635,7 +2635,7 @@
       </c>
       <c r="C31" s="3" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D31" s="3" t="inlineStr">
@@ -2644,7 +2644,7 @@
         </is>
       </c>
       <c r="E31" s="4" t="n">
-        <v>2154</v>
+        <v>2945</v>
       </c>
       <c r="F31" s="3" t="inlineStr">
         <is>
@@ -2700,12 +2700,12 @@
       </c>
       <c r="B32" s="3" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>6</t>
         </is>
       </c>
       <c r="C32" s="3" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="D32" s="3" t="inlineStr">
@@ -2714,7 +2714,7 @@
         </is>
       </c>
       <c r="E32" s="4" t="n">
-        <v>2945</v>
+        <v>2154</v>
       </c>
       <c r="F32" s="3" t="inlineStr">
         <is>
@@ -2775,7 +2775,7 @@
       </c>
       <c r="C33" s="3" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D33" s="3" t="inlineStr">
@@ -2784,7 +2784,7 @@
         </is>
       </c>
       <c r="E33" s="4" t="n">
-        <v>2154</v>
+        <v>2945</v>
       </c>
       <c r="F33" s="3" t="inlineStr">
         <is>
@@ -2840,12 +2840,12 @@
       </c>
       <c r="B34" s="3" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>5</t>
         </is>
       </c>
       <c r="C34" s="3" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="D34" s="3" t="inlineStr">
@@ -2854,7 +2854,7 @@
         </is>
       </c>
       <c r="E34" s="4" t="n">
-        <v>2945</v>
+        <v>2154</v>
       </c>
       <c r="F34" s="3" t="inlineStr">
         <is>
@@ -2915,7 +2915,7 @@
       </c>
       <c r="C35" s="3" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D35" s="3" t="inlineStr">
@@ -2924,7 +2924,7 @@
         </is>
       </c>
       <c r="E35" s="4" t="n">
-        <v>2154</v>
+        <v>2945</v>
       </c>
       <c r="F35" s="3" t="inlineStr">
         <is>
@@ -2980,12 +2980,12 @@
       </c>
       <c r="B36" s="3" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="C36" s="3" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="D36" s="3" t="inlineStr">
@@ -2994,7 +2994,7 @@
         </is>
       </c>
       <c r="E36" s="4" t="n">
-        <v>2945</v>
+        <v>2154</v>
       </c>
       <c r="F36" s="3" t="inlineStr">
         <is>
@@ -3055,7 +3055,7 @@
       </c>
       <c r="C37" s="3" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D37" s="3" t="inlineStr">
@@ -3064,7 +3064,7 @@
         </is>
       </c>
       <c r="E37" s="4" t="n">
-        <v>2154</v>
+        <v>2945</v>
       </c>
       <c r="F37" s="3" t="inlineStr">
         <is>
@@ -3120,12 +3120,12 @@
       </c>
       <c r="B38" s="3" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="C38" s="3" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="D38" s="3" t="inlineStr">
@@ -3134,7 +3134,7 @@
         </is>
       </c>
       <c r="E38" s="4" t="n">
-        <v>2945</v>
+        <v>2075</v>
       </c>
       <c r="F38" s="3" t="inlineStr">
         <is>
@@ -3195,7 +3195,7 @@
       </c>
       <c r="C39" s="3" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D39" s="3" t="inlineStr">
@@ -3204,7 +3204,7 @@
         </is>
       </c>
       <c r="E39" s="4" t="n">
-        <v>2075</v>
+        <v>2876</v>
       </c>
       <c r="F39" s="3" t="inlineStr">
         <is>
@@ -3255,17 +3255,17 @@
     <row r="40">
       <c r="A40" s="3" t="inlineStr">
         <is>
-          <t>1号及2号</t>
+          <t>3号及5号</t>
         </is>
       </c>
       <c r="B40" s="3" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>23</t>
         </is>
       </c>
       <c r="C40" s="3" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="D40" s="3" t="inlineStr">
@@ -3274,27 +3274,23 @@
         </is>
       </c>
       <c r="E40" s="4" t="n">
-        <v>2876</v>
+        <v>2664</v>
       </c>
       <c r="F40" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>已售</t>
         </is>
       </c>
       <c r="G40" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H40" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="I40" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+          <t>2021-05-11</t>
+        </is>
+      </c>
+      <c r="H40" s="5" t="n">
+        <v>344106000</v>
+      </c>
+      <c r="I40" s="5" t="n">
+        <v>129169</v>
       </c>
       <c r="J40" s="3" t="inlineStr">
         <is>
@@ -3330,12 +3326,12 @@
       </c>
       <c r="B41" s="3" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>22</t>
         </is>
       </c>
       <c r="C41" s="3" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="D41" s="3" t="inlineStr">
@@ -3344,7 +3340,7 @@
         </is>
       </c>
       <c r="E41" s="4" t="n">
-        <v>2664</v>
+        <v>2109</v>
       </c>
       <c r="F41" s="3" t="inlineStr">
         <is>
@@ -3353,14 +3349,14 @@
       </c>
       <c r="G41" s="3" t="inlineStr">
         <is>
-          <t>2021-05-11</t>
+          <t>2021-11-24</t>
         </is>
       </c>
       <c r="H41" s="5" t="n">
-        <v>344106000</v>
+        <v>186000000</v>
       </c>
       <c r="I41" s="5" t="n">
-        <v>129169</v>
+        <v>88193</v>
       </c>
       <c r="J41" s="3" t="inlineStr">
         <is>
@@ -3401,7 +3397,7 @@
       </c>
       <c r="C42" s="3" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="D42" s="3" t="inlineStr">
@@ -3410,7 +3406,7 @@
         </is>
       </c>
       <c r="E42" s="4" t="n">
-        <v>2109</v>
+        <v>2133</v>
       </c>
       <c r="F42" s="3" t="inlineStr">
         <is>
@@ -3423,10 +3419,10 @@
         </is>
       </c>
       <c r="H42" s="5" t="n">
-        <v>186000000</v>
+        <v>200000000</v>
       </c>
       <c r="I42" s="5" t="n">
-        <v>88193</v>
+        <v>93765</v>
       </c>
       <c r="J42" s="3" t="inlineStr">
         <is>
@@ -3462,12 +3458,12 @@
       </c>
       <c r="B43" s="3" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>21</t>
         </is>
       </c>
       <c r="C43" s="3" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="D43" s="3" t="inlineStr">
@@ -3476,23 +3472,27 @@
         </is>
       </c>
       <c r="E43" s="4" t="n">
-        <v>2133</v>
+        <v>2166</v>
       </c>
       <c r="F43" s="3" t="inlineStr">
         <is>
-          <t>已售</t>
+          <t>待售</t>
         </is>
       </c>
       <c r="G43" s="3" t="inlineStr">
         <is>
-          <t>2021-11-24</t>
-        </is>
-      </c>
-      <c r="H43" s="5" t="n">
-        <v>200000000</v>
-      </c>
-      <c r="I43" s="5" t="n">
-        <v>93765</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H43" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="I43" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
       </c>
       <c r="J43" s="3" t="inlineStr">
         <is>
@@ -3533,7 +3533,7 @@
       </c>
       <c r="C44" s="3" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="D44" s="3" t="inlineStr">
@@ -3542,7 +3542,7 @@
         </is>
       </c>
       <c r="E44" s="4" t="n">
-        <v>2166</v>
+        <v>2193</v>
       </c>
       <c r="F44" s="3" t="inlineStr">
         <is>
@@ -3598,12 +3598,12 @@
       </c>
       <c r="B45" s="3" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>20</t>
         </is>
       </c>
       <c r="C45" s="3" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="D45" s="3" t="inlineStr">
@@ -3612,7 +3612,7 @@
         </is>
       </c>
       <c r="E45" s="4" t="n">
-        <v>2193</v>
+        <v>2166</v>
       </c>
       <c r="F45" s="3" t="inlineStr">
         <is>
@@ -3673,7 +3673,7 @@
       </c>
       <c r="C46" s="3" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="D46" s="3" t="inlineStr">
@@ -3682,7 +3682,7 @@
         </is>
       </c>
       <c r="E46" s="4" t="n">
-        <v>2166</v>
+        <v>2193</v>
       </c>
       <c r="F46" s="3" t="inlineStr">
         <is>
@@ -3738,12 +3738,12 @@
       </c>
       <c r="B47" s="3" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>19</t>
         </is>
       </c>
       <c r="C47" s="3" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="D47" s="3" t="inlineStr">
@@ -3752,7 +3752,7 @@
         </is>
       </c>
       <c r="E47" s="4" t="n">
-        <v>2193</v>
+        <v>2166</v>
       </c>
       <c r="F47" s="3" t="inlineStr">
         <is>
@@ -3813,7 +3813,7 @@
       </c>
       <c r="C48" s="3" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="D48" s="3" t="inlineStr">
@@ -3822,27 +3822,23 @@
         </is>
       </c>
       <c r="E48" s="4" t="n">
-        <v>2166</v>
+        <v>2133</v>
       </c>
       <c r="F48" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>已售</t>
         </is>
       </c>
       <c r="G48" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H48" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="I48" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+          <t>2022-01-07</t>
+        </is>
+      </c>
+      <c r="H48" s="5" t="n">
+        <v>176800000</v>
+      </c>
+      <c r="I48" s="5" t="n">
+        <v>82888</v>
       </c>
       <c r="J48" s="3" t="inlineStr">
         <is>
@@ -3878,12 +3874,12 @@
       </c>
       <c r="B49" s="3" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>18</t>
         </is>
       </c>
       <c r="C49" s="3" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="D49" s="3" t="inlineStr">
@@ -3892,23 +3888,27 @@
         </is>
       </c>
       <c r="E49" s="4" t="n">
-        <v>2133</v>
+        <v>2166</v>
       </c>
       <c r="F49" s="3" t="inlineStr">
         <is>
-          <t>已售</t>
+          <t>待售</t>
         </is>
       </c>
       <c r="G49" s="3" t="inlineStr">
         <is>
-          <t>2022-01-07</t>
-        </is>
-      </c>
-      <c r="H49" s="5" t="n">
-        <v>176800000</v>
-      </c>
-      <c r="I49" s="5" t="n">
-        <v>82888</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H49" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="I49" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
       </c>
       <c r="J49" s="3" t="inlineStr">
         <is>
@@ -3949,7 +3949,7 @@
       </c>
       <c r="C50" s="3" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="D50" s="3" t="inlineStr">
@@ -3958,27 +3958,23 @@
         </is>
       </c>
       <c r="E50" s="4" t="n">
-        <v>2166</v>
+        <v>2133</v>
       </c>
       <c r="F50" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>已售</t>
         </is>
       </c>
       <c r="G50" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H50" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="I50" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+          <t>2021-06-30</t>
+        </is>
+      </c>
+      <c r="H50" s="5" t="n">
+        <v>172000000</v>
+      </c>
+      <c r="I50" s="5" t="n">
+        <v>80638</v>
       </c>
       <c r="J50" s="3" t="inlineStr">
         <is>
@@ -4014,12 +4010,12 @@
       </c>
       <c r="B51" s="3" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>17</t>
         </is>
       </c>
       <c r="C51" s="3" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="D51" s="3" t="inlineStr">
@@ -4028,23 +4024,27 @@
         </is>
       </c>
       <c r="E51" s="4" t="n">
-        <v>2133</v>
+        <v>2166</v>
       </c>
       <c r="F51" s="3" t="inlineStr">
         <is>
-          <t>已售</t>
+          <t>待售</t>
         </is>
       </c>
       <c r="G51" s="3" t="inlineStr">
         <is>
-          <t>2021-06-30</t>
-        </is>
-      </c>
-      <c r="H51" s="5" t="n">
-        <v>172000000</v>
-      </c>
-      <c r="I51" s="5" t="n">
-        <v>80638</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H51" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="I51" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
       </c>
       <c r="J51" s="3" t="inlineStr">
         <is>
@@ -4085,7 +4085,7 @@
       </c>
       <c r="C52" s="3" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="D52" s="3" t="inlineStr">
@@ -4094,27 +4094,23 @@
         </is>
       </c>
       <c r="E52" s="4" t="n">
-        <v>2166</v>
+        <v>2133</v>
       </c>
       <c r="F52" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>已售</t>
         </is>
       </c>
       <c r="G52" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H52" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="I52" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+          <t>2022-03-01</t>
+        </is>
+      </c>
+      <c r="H52" s="5" t="n">
+        <v>167800000</v>
+      </c>
+      <c r="I52" s="5" t="n">
+        <v>78669</v>
       </c>
       <c r="J52" s="3" t="inlineStr">
         <is>
@@ -4150,12 +4146,12 @@
       </c>
       <c r="B53" s="3" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>16</t>
         </is>
       </c>
       <c r="C53" s="3" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="D53" s="3" t="inlineStr">
@@ -4164,23 +4160,27 @@
         </is>
       </c>
       <c r="E53" s="4" t="n">
-        <v>2133</v>
+        <v>2166</v>
       </c>
       <c r="F53" s="3" t="inlineStr">
         <is>
-          <t>已售</t>
+          <t>待售</t>
         </is>
       </c>
       <c r="G53" s="3" t="inlineStr">
         <is>
-          <t>2022-03-01</t>
-        </is>
-      </c>
-      <c r="H53" s="5" t="n">
-        <v>167800000</v>
-      </c>
-      <c r="I53" s="5" t="n">
-        <v>78669</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H53" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="I53" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
       </c>
       <c r="J53" s="3" t="inlineStr">
         <is>
@@ -4221,7 +4221,7 @@
       </c>
       <c r="C54" s="3" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="D54" s="3" t="inlineStr">
@@ -4230,27 +4230,23 @@
         </is>
       </c>
       <c r="E54" s="4" t="n">
-        <v>2166</v>
+        <v>2133</v>
       </c>
       <c r="F54" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>已售</t>
         </is>
       </c>
       <c r="G54" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H54" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="I54" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+          <t>2025-08-21</t>
+        </is>
+      </c>
+      <c r="H54" s="5" t="n">
+        <v>162000000</v>
+      </c>
+      <c r="I54" s="5" t="n">
+        <v>75949</v>
       </c>
       <c r="J54" s="3" t="inlineStr">
         <is>
@@ -4286,12 +4282,12 @@
       </c>
       <c r="B55" s="3" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>15</t>
         </is>
       </c>
       <c r="C55" s="3" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="D55" s="3" t="inlineStr">
@@ -4300,23 +4296,27 @@
         </is>
       </c>
       <c r="E55" s="4" t="n">
-        <v>2133</v>
+        <v>2166</v>
       </c>
       <c r="F55" s="3" t="inlineStr">
         <is>
-          <t>已售</t>
+          <t>待售</t>
         </is>
       </c>
       <c r="G55" s="3" t="inlineStr">
         <is>
-          <t>2025-08-21</t>
-        </is>
-      </c>
-      <c r="H55" s="5" t="n">
-        <v>162000000</v>
-      </c>
-      <c r="I55" s="5" t="n">
-        <v>75949</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H55" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="I55" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
       </c>
       <c r="J55" s="3" t="inlineStr">
         <is>
@@ -4357,7 +4357,7 @@
       </c>
       <c r="C56" s="3" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="D56" s="3" t="inlineStr">
@@ -4366,27 +4366,23 @@
         </is>
       </c>
       <c r="E56" s="4" t="n">
-        <v>2166</v>
+        <v>2133</v>
       </c>
       <c r="F56" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>已售</t>
         </is>
       </c>
       <c r="G56" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H56" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="I56" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+          <t>2024-12-10</t>
+        </is>
+      </c>
+      <c r="H56" s="5" t="n">
+        <v>156000000</v>
+      </c>
+      <c r="I56" s="5" t="n">
+        <v>73136</v>
       </c>
       <c r="J56" s="3" t="inlineStr">
         <is>
@@ -4422,12 +4418,12 @@
       </c>
       <c r="B57" s="3" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>12</t>
         </is>
       </c>
       <c r="C57" s="3" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="D57" s="3" t="inlineStr">
@@ -4436,23 +4432,27 @@
         </is>
       </c>
       <c r="E57" s="4" t="n">
-        <v>2133</v>
+        <v>2166</v>
       </c>
       <c r="F57" s="3" t="inlineStr">
         <is>
-          <t>已售</t>
+          <t>待售</t>
         </is>
       </c>
       <c r="G57" s="3" t="inlineStr">
         <is>
-          <t>2024-12-10</t>
-        </is>
-      </c>
-      <c r="H57" s="5" t="n">
-        <v>156000000</v>
-      </c>
-      <c r="I57" s="5" t="n">
-        <v>73136</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H57" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="I57" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
       </c>
       <c r="J57" s="3" t="inlineStr">
         <is>
@@ -4493,7 +4493,7 @@
       </c>
       <c r="C58" s="3" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="D58" s="3" t="inlineStr">
@@ -4502,27 +4502,23 @@
         </is>
       </c>
       <c r="E58" s="4" t="n">
-        <v>2166</v>
+        <v>2133</v>
       </c>
       <c r="F58" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>已售</t>
         </is>
       </c>
       <c r="G58" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H58" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="I58" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+          <t>2023-05-05</t>
+        </is>
+      </c>
+      <c r="H58" s="5" t="n">
+        <v>153800000</v>
+      </c>
+      <c r="I58" s="5" t="n">
+        <v>72105</v>
       </c>
       <c r="J58" s="3" t="inlineStr">
         <is>
@@ -4558,12 +4554,12 @@
       </c>
       <c r="B59" s="3" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>11</t>
         </is>
       </c>
       <c r="C59" s="3" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="D59" s="3" t="inlineStr">
@@ -4572,23 +4568,27 @@
         </is>
       </c>
       <c r="E59" s="4" t="n">
-        <v>2133</v>
+        <v>2166</v>
       </c>
       <c r="F59" s="3" t="inlineStr">
         <is>
-          <t>已售</t>
+          <t>待售</t>
         </is>
       </c>
       <c r="G59" s="3" t="inlineStr">
         <is>
-          <t>2023-05-05</t>
-        </is>
-      </c>
-      <c r="H59" s="5" t="n">
-        <v>153800000</v>
-      </c>
-      <c r="I59" s="5" t="n">
-        <v>72105</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H59" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="I59" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
       </c>
       <c r="J59" s="3" t="inlineStr">
         <is>
@@ -4629,7 +4629,7 @@
       </c>
       <c r="C60" s="3" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="D60" s="3" t="inlineStr">
@@ -4638,27 +4638,23 @@
         </is>
       </c>
       <c r="E60" s="4" t="n">
-        <v>2166</v>
+        <v>2133</v>
       </c>
       <c r="F60" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>已售</t>
         </is>
       </c>
       <c r="G60" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H60" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="I60" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="H60" s="5" t="n">
+        <v>151000000</v>
+      </c>
+      <c r="I60" s="5" t="n">
+        <v>70792</v>
       </c>
       <c r="J60" s="3" t="inlineStr">
         <is>
@@ -4694,12 +4690,12 @@
       </c>
       <c r="B61" s="3" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>10</t>
         </is>
       </c>
       <c r="C61" s="3" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="D61" s="3" t="inlineStr">
@@ -4708,23 +4704,27 @@
         </is>
       </c>
       <c r="E61" s="4" t="n">
-        <v>2133</v>
+        <v>2166</v>
       </c>
       <c r="F61" s="3" t="inlineStr">
         <is>
-          <t>已售</t>
+          <t>待售</t>
         </is>
       </c>
       <c r="G61" s="3" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
-        </is>
-      </c>
-      <c r="H61" s="5" t="n">
-        <v>151000000</v>
-      </c>
-      <c r="I61" s="5" t="n">
-        <v>70792</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H61" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="I61" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
       </c>
       <c r="J61" s="3" t="inlineStr">
         <is>
@@ -4765,7 +4765,7 @@
       </c>
       <c r="C62" s="3" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="D62" s="3" t="inlineStr">
@@ -4774,27 +4774,23 @@
         </is>
       </c>
       <c r="E62" s="4" t="n">
-        <v>2166</v>
+        <v>2133</v>
       </c>
       <c r="F62" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>已售</t>
         </is>
       </c>
       <c r="G62" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H62" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="I62" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+          <t>2025-06-19</t>
+        </is>
+      </c>
+      <c r="H62" s="5" t="n">
+        <v>148000000</v>
+      </c>
+      <c r="I62" s="5" t="n">
+        <v>69386</v>
       </c>
       <c r="J62" s="3" t="inlineStr">
         <is>
@@ -4830,12 +4826,12 @@
       </c>
       <c r="B63" s="3" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>9</t>
         </is>
       </c>
       <c r="C63" s="3" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="D63" s="3" t="inlineStr">
@@ -4844,23 +4840,27 @@
         </is>
       </c>
       <c r="E63" s="4" t="n">
-        <v>2133</v>
+        <v>2166</v>
       </c>
       <c r="F63" s="3" t="inlineStr">
         <is>
-          <t>已售</t>
+          <t>待售</t>
         </is>
       </c>
       <c r="G63" s="3" t="inlineStr">
         <is>
-          <t>2025-06-19</t>
-        </is>
-      </c>
-      <c r="H63" s="5" t="n">
-        <v>148000000</v>
-      </c>
-      <c r="I63" s="5" t="n">
-        <v>69386</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H63" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="I63" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
       </c>
       <c r="J63" s="3" t="inlineStr">
         <is>
@@ -4901,7 +4901,7 @@
       </c>
       <c r="C64" s="3" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="D64" s="3" t="inlineStr">
@@ -4910,7 +4910,7 @@
         </is>
       </c>
       <c r="E64" s="4" t="n">
-        <v>2166</v>
+        <v>2193</v>
       </c>
       <c r="F64" s="3" t="inlineStr">
         <is>
@@ -4966,12 +4966,12 @@
       </c>
       <c r="B65" s="3" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>8</t>
         </is>
       </c>
       <c r="C65" s="3" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="D65" s="3" t="inlineStr">
@@ -4980,7 +4980,7 @@
         </is>
       </c>
       <c r="E65" s="4" t="n">
-        <v>2193</v>
+        <v>2166</v>
       </c>
       <c r="F65" s="3" t="inlineStr">
         <is>
@@ -5041,7 +5041,7 @@
       </c>
       <c r="C66" s="3" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="D66" s="3" t="inlineStr">
@@ -5050,7 +5050,7 @@
         </is>
       </c>
       <c r="E66" s="4" t="n">
-        <v>2166</v>
+        <v>2193</v>
       </c>
       <c r="F66" s="3" t="inlineStr">
         <is>
@@ -5106,12 +5106,12 @@
       </c>
       <c r="B67" s="3" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7</t>
         </is>
       </c>
       <c r="C67" s="3" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="D67" s="3" t="inlineStr">
@@ -5120,7 +5120,7 @@
         </is>
       </c>
       <c r="E67" s="4" t="n">
-        <v>2193</v>
+        <v>2166</v>
       </c>
       <c r="F67" s="3" t="inlineStr">
         <is>
@@ -5181,7 +5181,7 @@
       </c>
       <c r="C68" s="3" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="D68" s="3" t="inlineStr">
@@ -5190,7 +5190,7 @@
         </is>
       </c>
       <c r="E68" s="4" t="n">
-        <v>2166</v>
+        <v>2193</v>
       </c>
       <c r="F68" s="3" t="inlineStr">
         <is>
@@ -5246,12 +5246,12 @@
       </c>
       <c r="B69" s="3" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>6</t>
         </is>
       </c>
       <c r="C69" s="3" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="D69" s="3" t="inlineStr">
@@ -5260,7 +5260,7 @@
         </is>
       </c>
       <c r="E69" s="4" t="n">
-        <v>2193</v>
+        <v>2166</v>
       </c>
       <c r="F69" s="3" t="inlineStr">
         <is>
@@ -5321,7 +5321,7 @@
       </c>
       <c r="C70" s="3" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="D70" s="3" t="inlineStr">
@@ -5330,7 +5330,7 @@
         </is>
       </c>
       <c r="E70" s="4" t="n">
-        <v>2166</v>
+        <v>2193</v>
       </c>
       <c r="F70" s="3" t="inlineStr">
         <is>
@@ -5386,12 +5386,12 @@
       </c>
       <c r="B71" s="3" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>5</t>
         </is>
       </c>
       <c r="C71" s="3" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="D71" s="3" t="inlineStr">
@@ -5400,7 +5400,7 @@
         </is>
       </c>
       <c r="E71" s="4" t="n">
-        <v>2193</v>
+        <v>2166</v>
       </c>
       <c r="F71" s="3" t="inlineStr">
         <is>
@@ -5461,7 +5461,7 @@
       </c>
       <c r="C72" s="3" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="D72" s="3" t="inlineStr">
@@ -5470,7 +5470,7 @@
         </is>
       </c>
       <c r="E72" s="4" t="n">
-        <v>2166</v>
+        <v>2193</v>
       </c>
       <c r="F72" s="3" t="inlineStr">
         <is>
@@ -5526,21 +5526,21 @@
       </c>
       <c r="B73" s="3" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="C73" s="3" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="C73" s="3" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="D73" s="3" t="inlineStr">
         <is>
           <t>4+房</t>
         </is>
       </c>
       <c r="E73" s="4" t="n">
-        <v>2193</v>
+        <v>2166</v>
       </c>
       <c r="F73" s="3" t="inlineStr">
         <is>
@@ -5601,7 +5601,7 @@
       </c>
       <c r="C74" s="3" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="D74" s="3" t="inlineStr">
@@ -5610,7 +5610,7 @@
         </is>
       </c>
       <c r="E74" s="4" t="n">
-        <v>2166</v>
+        <v>2193</v>
       </c>
       <c r="F74" s="3" t="inlineStr">
         <is>
@@ -5666,12 +5666,12 @@
       </c>
       <c r="B75" s="3" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="C75" s="3" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="D75" s="3" t="inlineStr">
@@ -5680,7 +5680,7 @@
         </is>
       </c>
       <c r="E75" s="4" t="n">
-        <v>2193</v>
+        <v>2166</v>
       </c>
       <c r="F75" s="3" t="inlineStr">
         <is>
@@ -5741,7 +5741,7 @@
       </c>
       <c r="C76" s="3" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="D76" s="3" t="inlineStr">
@@ -5750,7 +5750,7 @@
         </is>
       </c>
       <c r="E76" s="4" t="n">
-        <v>2166</v>
+        <v>2193</v>
       </c>
       <c r="F76" s="3" t="inlineStr">
         <is>
@@ -5806,12 +5806,12 @@
       </c>
       <c r="B77" s="3" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="C77" s="3" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="D77" s="3" t="inlineStr">
@@ -5820,27 +5820,23 @@
         </is>
       </c>
       <c r="E77" s="4" t="n">
-        <v>2193</v>
+        <v>2029</v>
       </c>
       <c r="F77" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>已售</t>
         </is>
       </c>
       <c r="G77" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H77" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="I77" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+          <t>2025-10-03</t>
+        </is>
+      </c>
+      <c r="H77" s="5" t="n">
+        <v>125600000</v>
+      </c>
+      <c r="I77" s="5" t="n">
+        <v>61902</v>
       </c>
       <c r="J77" s="3" t="inlineStr">
         <is>
@@ -5881,7 +5877,7 @@
       </c>
       <c r="C78" s="3" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="D78" s="3" t="inlineStr">
@@ -5890,7 +5886,7 @@
         </is>
       </c>
       <c r="E78" s="4" t="n">
-        <v>2029</v>
+        <v>2065</v>
       </c>
       <c r="F78" s="3" t="inlineStr">
         <is>
@@ -5899,14 +5895,14 @@
       </c>
       <c r="G78" s="3" t="inlineStr">
         <is>
-          <t>2025-10-03</t>
+          <t>2025-04-25</t>
         </is>
       </c>
       <c r="H78" s="5" t="n">
-        <v>125600000</v>
+        <v>126950000</v>
       </c>
       <c r="I78" s="5" t="n">
-        <v>61902</v>
+        <v>61477</v>
       </c>
       <c r="J78" s="3" t="inlineStr">
         <is>
@@ -5937,17 +5933,17 @@
     <row r="79">
       <c r="A79" s="3" t="inlineStr">
         <is>
-          <t>3号及5号</t>
+          <t>6号及7号</t>
         </is>
       </c>
       <c r="B79" s="3" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>23</t>
         </is>
       </c>
       <c r="C79" s="3" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>6</t>
         </is>
       </c>
       <c r="D79" s="3" t="inlineStr">
@@ -5956,7 +5952,7 @@
         </is>
       </c>
       <c r="E79" s="4" t="n">
-        <v>2065</v>
+        <v>2927</v>
       </c>
       <c r="F79" s="3" t="inlineStr">
         <is>
@@ -5965,14 +5961,14 @@
       </c>
       <c r="G79" s="3" t="inlineStr">
         <is>
-          <t>2025-04-25</t>
+          <t>2021-04-16</t>
         </is>
       </c>
       <c r="H79" s="5" t="n">
-        <v>126950000</v>
+        <v>377370000</v>
       </c>
       <c r="I79" s="5" t="n">
-        <v>61477</v>
+        <v>128927</v>
       </c>
       <c r="J79" s="3" t="inlineStr">
         <is>
@@ -6008,12 +6004,12 @@
       </c>
       <c r="B80" s="3" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>22</t>
         </is>
       </c>
       <c r="C80" s="3" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="D80" s="3" t="inlineStr">
@@ -6022,7 +6018,7 @@
         </is>
       </c>
       <c r="E80" s="4" t="n">
-        <v>2927</v>
+        <v>2256</v>
       </c>
       <c r="F80" s="3" t="inlineStr">
         <is>
@@ -6031,14 +6027,14 @@
       </c>
       <c r="G80" s="3" t="inlineStr">
         <is>
-          <t>2021-04-16</t>
+          <t>2021-08-03</t>
         </is>
       </c>
       <c r="H80" s="5" t="n">
-        <v>377370000</v>
+        <v>208500000</v>
       </c>
       <c r="I80" s="5" t="n">
-        <v>128927</v>
+        <v>92420</v>
       </c>
       <c r="J80" s="3" t="inlineStr">
         <is>
@@ -6079,7 +6075,7 @@
       </c>
       <c r="C81" s="3" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>6</t>
         </is>
       </c>
       <c r="D81" s="3" t="inlineStr">
@@ -6088,7 +6084,7 @@
         </is>
       </c>
       <c r="E81" s="4" t="n">
-        <v>2256</v>
+        <v>2112</v>
       </c>
       <c r="F81" s="3" t="inlineStr">
         <is>
@@ -6101,10 +6097,10 @@
         </is>
       </c>
       <c r="H81" s="5" t="n">
-        <v>208500000</v>
+        <v>181500000</v>
       </c>
       <c r="I81" s="5" t="n">
-        <v>92420</v>
+        <v>85938</v>
       </c>
       <c r="J81" s="3" t="inlineStr">
         <is>
@@ -6140,12 +6136,12 @@
       </c>
       <c r="B82" s="3" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>21</t>
         </is>
       </c>
       <c r="C82" s="3" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="D82" s="3" t="inlineStr">
@@ -6154,7 +6150,7 @@
         </is>
       </c>
       <c r="E82" s="4" t="n">
-        <v>2112</v>
+        <v>2256</v>
       </c>
       <c r="F82" s="3" t="inlineStr">
         <is>
@@ -6163,14 +6159,14 @@
       </c>
       <c r="G82" s="3" t="inlineStr">
         <is>
-          <t>2021-08-03</t>
+          <t>2022-06-02</t>
         </is>
       </c>
       <c r="H82" s="5" t="n">
-        <v>181500000</v>
+        <v>203888000</v>
       </c>
       <c r="I82" s="5" t="n">
-        <v>85938</v>
+        <v>90376</v>
       </c>
       <c r="J82" s="3" t="inlineStr">
         <is>
@@ -6211,7 +6207,7 @@
       </c>
       <c r="C83" s="3" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>6</t>
         </is>
       </c>
       <c r="D83" s="3" t="inlineStr">
@@ -6220,7 +6216,7 @@
         </is>
       </c>
       <c r="E83" s="4" t="n">
-        <v>2256</v>
+        <v>2112</v>
       </c>
       <c r="F83" s="3" t="inlineStr">
         <is>
@@ -6233,10 +6229,10 @@
         </is>
       </c>
       <c r="H83" s="5" t="n">
-        <v>203888000</v>
+        <v>190110000</v>
       </c>
       <c r="I83" s="5" t="n">
-        <v>90376</v>
+        <v>90014</v>
       </c>
       <c r="J83" s="3" t="inlineStr">
         <is>
@@ -6272,37 +6268,41 @@
       </c>
       <c r="B84" s="3" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>20</t>
         </is>
       </c>
       <c r="C84" s="3" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="D84" s="3" t="inlineStr">
         <is>
-          <t>4+房</t>
+          <t>1房</t>
         </is>
       </c>
       <c r="E84" s="4" t="n">
-        <v>2112</v>
+        <v>2316</v>
       </c>
       <c r="F84" s="3" t="inlineStr">
         <is>
-          <t>已售</t>
+          <t>待售</t>
         </is>
       </c>
       <c r="G84" s="3" t="inlineStr">
         <is>
-          <t>2022-06-02</t>
-        </is>
-      </c>
-      <c r="H84" s="5" t="n">
-        <v>190110000</v>
-      </c>
-      <c r="I84" s="5" t="n">
-        <v>90014</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H84" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="I84" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
       </c>
       <c r="J84" s="3" t="inlineStr">
         <is>
@@ -6343,16 +6343,16 @@
       </c>
       <c r="C85" s="3" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>6</t>
         </is>
       </c>
       <c r="D85" s="3" t="inlineStr">
         <is>
-          <t>1房</t>
+          <t>2房</t>
         </is>
       </c>
       <c r="E85" s="4" t="n">
-        <v>2316</v>
+        <v>2169</v>
       </c>
       <c r="F85" s="3" t="inlineStr">
         <is>
@@ -6408,41 +6408,37 @@
       </c>
       <c r="B86" s="3" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>19</t>
         </is>
       </c>
       <c r="C86" s="3" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="D86" s="3" t="inlineStr">
         <is>
-          <t>2房</t>
+          <t>4+房</t>
         </is>
       </c>
       <c r="E86" s="4" t="n">
-        <v>2169</v>
+        <v>2256</v>
       </c>
       <c r="F86" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>已售</t>
         </is>
       </c>
       <c r="G86" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H86" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="I86" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+          <t>2021-08-16</t>
+        </is>
+      </c>
+      <c r="H86" s="5" t="n">
+        <v>190380000</v>
+      </c>
+      <c r="I86" s="5" t="n">
+        <v>84388</v>
       </c>
       <c r="J86" s="3" t="inlineStr">
         <is>
@@ -6483,7 +6479,7 @@
       </c>
       <c r="C87" s="3" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>6</t>
         </is>
       </c>
       <c r="D87" s="3" t="inlineStr">
@@ -6492,7 +6488,7 @@
         </is>
       </c>
       <c r="E87" s="4" t="n">
-        <v>2256</v>
+        <v>2112</v>
       </c>
       <c r="F87" s="3" t="inlineStr">
         <is>
@@ -6501,14 +6497,14 @@
       </c>
       <c r="G87" s="3" t="inlineStr">
         <is>
-          <t>2021-08-16</t>
+          <t>2021-11-16</t>
         </is>
       </c>
       <c r="H87" s="5" t="n">
-        <v>190380000</v>
+        <v>172000000</v>
       </c>
       <c r="I87" s="5" t="n">
-        <v>84388</v>
+        <v>81439</v>
       </c>
       <c r="J87" s="3" t="inlineStr">
         <is>
@@ -6544,12 +6540,12 @@
       </c>
       <c r="B88" s="3" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>18</t>
         </is>
       </c>
       <c r="C88" s="3" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="D88" s="3" t="inlineStr">
@@ -6558,7 +6554,7 @@
         </is>
       </c>
       <c r="E88" s="4" t="n">
-        <v>2112</v>
+        <v>2256</v>
       </c>
       <c r="F88" s="3" t="inlineStr">
         <is>
@@ -6567,14 +6563,14 @@
       </c>
       <c r="G88" s="3" t="inlineStr">
         <is>
-          <t>2021-11-16</t>
+          <t>2021-10-21</t>
         </is>
       </c>
       <c r="H88" s="5" t="n">
-        <v>172000000</v>
+        <v>185233680</v>
       </c>
       <c r="I88" s="5" t="n">
-        <v>81439</v>
+        <v>82107</v>
       </c>
       <c r="J88" s="3" t="inlineStr">
         <is>
@@ -6615,7 +6611,7 @@
       </c>
       <c r="C89" s="3" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>6</t>
         </is>
       </c>
       <c r="D89" s="3" t="inlineStr">
@@ -6624,7 +6620,7 @@
         </is>
       </c>
       <c r="E89" s="4" t="n">
-        <v>2256</v>
+        <v>2112</v>
       </c>
       <c r="F89" s="3" t="inlineStr">
         <is>
@@ -6633,14 +6629,14 @@
       </c>
       <c r="G89" s="3" t="inlineStr">
         <is>
-          <t>2021-10-21</t>
+          <t>2022-01-31</t>
         </is>
       </c>
       <c r="H89" s="5" t="n">
-        <v>185233680</v>
+        <v>166800000</v>
       </c>
       <c r="I89" s="5" t="n">
-        <v>82107</v>
+        <v>78977</v>
       </c>
       <c r="J89" s="3" t="inlineStr">
         <is>
@@ -6676,12 +6672,12 @@
       </c>
       <c r="B90" s="3" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>17</t>
         </is>
       </c>
       <c r="C90" s="3" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="D90" s="3" t="inlineStr">
@@ -6690,7 +6686,7 @@
         </is>
       </c>
       <c r="E90" s="4" t="n">
-        <v>2112</v>
+        <v>2256</v>
       </c>
       <c r="F90" s="3" t="inlineStr">
         <is>
@@ -6699,14 +6695,14 @@
       </c>
       <c r="G90" s="3" t="inlineStr">
         <is>
-          <t>2022-01-31</t>
+          <t>2021-10-19</t>
         </is>
       </c>
       <c r="H90" s="5" t="n">
-        <v>166800000</v>
+        <v>180000000</v>
       </c>
       <c r="I90" s="5" t="n">
-        <v>78977</v>
+        <v>79787</v>
       </c>
       <c r="J90" s="3" t="inlineStr">
         <is>
@@ -6747,7 +6743,7 @@
       </c>
       <c r="C91" s="3" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>6</t>
         </is>
       </c>
       <c r="D91" s="3" t="inlineStr">
@@ -6756,23 +6752,27 @@
         </is>
       </c>
       <c r="E91" s="4" t="n">
-        <v>2256</v>
+        <v>2169</v>
       </c>
       <c r="F91" s="3" t="inlineStr">
         <is>
-          <t>已售</t>
+          <t>待售</t>
         </is>
       </c>
       <c r="G91" s="3" t="inlineStr">
         <is>
-          <t>2021-10-19</t>
-        </is>
-      </c>
-      <c r="H91" s="5" t="n">
-        <v>180000000</v>
-      </c>
-      <c r="I91" s="5" t="n">
-        <v>79787</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H91" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="I91" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
       </c>
       <c r="J91" s="3" t="inlineStr">
         <is>
@@ -6808,12 +6808,12 @@
       </c>
       <c r="B92" s="3" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>16</t>
         </is>
       </c>
       <c r="C92" s="3" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="D92" s="3" t="inlineStr">
@@ -6822,27 +6822,23 @@
         </is>
       </c>
       <c r="E92" s="4" t="n">
-        <v>2169</v>
+        <v>2256</v>
       </c>
       <c r="F92" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>已售</t>
         </is>
       </c>
       <c r="G92" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H92" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="I92" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+          <t>2021-10-19</t>
+        </is>
+      </c>
+      <c r="H92" s="5" t="n">
+        <v>173600000</v>
+      </c>
+      <c r="I92" s="5" t="n">
+        <v>76950</v>
       </c>
       <c r="J92" s="3" t="inlineStr">
         <is>
@@ -6883,7 +6879,7 @@
       </c>
       <c r="C93" s="3" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>6</t>
         </is>
       </c>
       <c r="D93" s="3" t="inlineStr">
@@ -6892,7 +6888,7 @@
         </is>
       </c>
       <c r="E93" s="4" t="n">
-        <v>2256</v>
+        <v>2112</v>
       </c>
       <c r="F93" s="3" t="inlineStr">
         <is>
@@ -6901,14 +6897,14 @@
       </c>
       <c r="G93" s="3" t="inlineStr">
         <is>
-          <t>2021-10-19</t>
+          <t>2021-10-12</t>
         </is>
       </c>
       <c r="H93" s="5" t="n">
-        <v>173600000</v>
+        <v>159300000</v>
       </c>
       <c r="I93" s="5" t="n">
-        <v>76950</v>
+        <v>75426</v>
       </c>
       <c r="J93" s="3" t="inlineStr">
         <is>
@@ -6944,12 +6940,12 @@
       </c>
       <c r="B94" s="3" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>15</t>
         </is>
       </c>
       <c r="C94" s="3" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="D94" s="3" t="inlineStr">
@@ -6958,7 +6954,7 @@
         </is>
       </c>
       <c r="E94" s="4" t="n">
-        <v>2112</v>
+        <v>2256</v>
       </c>
       <c r="F94" s="3" t="inlineStr">
         <is>
@@ -6967,14 +6963,14 @@
       </c>
       <c r="G94" s="3" t="inlineStr">
         <is>
-          <t>2021-10-12</t>
+          <t>2021-04-27</t>
         </is>
       </c>
       <c r="H94" s="5" t="n">
-        <v>159300000</v>
+        <v>168000000</v>
       </c>
       <c r="I94" s="5" t="n">
-        <v>75426</v>
+        <v>74468</v>
       </c>
       <c r="J94" s="3" t="inlineStr">
         <is>
@@ -7015,7 +7011,7 @@
       </c>
       <c r="C95" s="3" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>6</t>
         </is>
       </c>
       <c r="D95" s="3" t="inlineStr">
@@ -7024,7 +7020,7 @@
         </is>
       </c>
       <c r="E95" s="4" t="n">
-        <v>2256</v>
+        <v>2112</v>
       </c>
       <c r="F95" s="3" t="inlineStr">
         <is>
@@ -7033,14 +7029,14 @@
       </c>
       <c r="G95" s="3" t="inlineStr">
         <is>
-          <t>2021-04-27</t>
+          <t>2021-09-10</t>
         </is>
       </c>
       <c r="H95" s="5" t="n">
-        <v>168000000</v>
+        <v>154800000</v>
       </c>
       <c r="I95" s="5" t="n">
-        <v>74468</v>
+        <v>73295</v>
       </c>
       <c r="J95" s="3" t="inlineStr">
         <is>
@@ -7076,12 +7072,12 @@
       </c>
       <c r="B96" s="3" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>12</t>
         </is>
       </c>
       <c r="C96" s="3" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="D96" s="3" t="inlineStr">
@@ -7090,23 +7086,27 @@
         </is>
       </c>
       <c r="E96" s="4" t="n">
-        <v>2112</v>
+        <v>2316</v>
       </c>
       <c r="F96" s="3" t="inlineStr">
         <is>
-          <t>已售</t>
+          <t>待售</t>
         </is>
       </c>
       <c r="G96" s="3" t="inlineStr">
         <is>
-          <t>2021-09-10</t>
-        </is>
-      </c>
-      <c r="H96" s="5" t="n">
-        <v>154800000</v>
-      </c>
-      <c r="I96" s="5" t="n">
-        <v>73295</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H96" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="I96" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
       </c>
       <c r="J96" s="3" t="inlineStr">
         <is>
@@ -7147,7 +7147,7 @@
       </c>
       <c r="C97" s="3" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>6</t>
         </is>
       </c>
       <c r="D97" s="3" t="inlineStr">
@@ -7156,27 +7156,23 @@
         </is>
       </c>
       <c r="E97" s="4" t="n">
-        <v>2316</v>
+        <v>2112</v>
       </c>
       <c r="F97" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>已售</t>
         </is>
       </c>
       <c r="G97" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H97" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="I97" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+          <t>2024-05-30</t>
+        </is>
+      </c>
+      <c r="H97" s="5" t="n">
+        <v>140000000</v>
+      </c>
+      <c r="I97" s="5" t="n">
+        <v>66288</v>
       </c>
       <c r="J97" s="3" t="inlineStr">
         <is>
@@ -7212,12 +7208,12 @@
       </c>
       <c r="B98" s="3" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>11</t>
         </is>
       </c>
       <c r="C98" s="3" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="D98" s="3" t="inlineStr">
@@ -7226,7 +7222,7 @@
         </is>
       </c>
       <c r="E98" s="4" t="n">
-        <v>2112</v>
+        <v>2256</v>
       </c>
       <c r="F98" s="3" t="inlineStr">
         <is>
@@ -7235,14 +7231,14 @@
       </c>
       <c r="G98" s="3" t="inlineStr">
         <is>
-          <t>2024-05-30</t>
+          <t>2023-04-03</t>
         </is>
       </c>
       <c r="H98" s="5" t="n">
-        <v>140000000</v>
+        <v>162800000</v>
       </c>
       <c r="I98" s="5" t="n">
-        <v>66288</v>
+        <v>72163</v>
       </c>
       <c r="J98" s="3" t="inlineStr">
         <is>
@@ -7283,7 +7279,7 @@
       </c>
       <c r="C99" s="3" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>6</t>
         </is>
       </c>
       <c r="D99" s="3" t="inlineStr">
@@ -7292,23 +7288,27 @@
         </is>
       </c>
       <c r="E99" s="4" t="n">
-        <v>2256</v>
+        <v>2169</v>
       </c>
       <c r="F99" s="3" t="inlineStr">
         <is>
-          <t>已售</t>
+          <t>待售</t>
         </is>
       </c>
       <c r="G99" s="3" t="inlineStr">
         <is>
-          <t>2023-04-03</t>
-        </is>
-      </c>
-      <c r="H99" s="5" t="n">
-        <v>162800000</v>
-      </c>
-      <c r="I99" s="5" t="n">
-        <v>72163</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H99" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="I99" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
       </c>
       <c r="J99" s="3" t="inlineStr">
         <is>
@@ -7344,12 +7344,12 @@
       </c>
       <c r="B100" s="3" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>10</t>
         </is>
       </c>
       <c r="C100" s="3" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="D100" s="3" t="inlineStr">
@@ -7358,27 +7358,23 @@
         </is>
       </c>
       <c r="E100" s="4" t="n">
-        <v>2169</v>
+        <v>2256</v>
       </c>
       <c r="F100" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>已售</t>
         </is>
       </c>
       <c r="G100" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H100" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="I100" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+          <t>2023-03-21</t>
+        </is>
+      </c>
+      <c r="H100" s="5" t="n">
+        <v>152800000</v>
+      </c>
+      <c r="I100" s="5" t="n">
+        <v>67730</v>
       </c>
       <c r="J100" s="3" t="inlineStr">
         <is>
@@ -7419,7 +7415,7 @@
       </c>
       <c r="C101" s="3" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>6</t>
         </is>
       </c>
       <c r="D101" s="3" t="inlineStr">
@@ -7428,7 +7424,7 @@
         </is>
       </c>
       <c r="E101" s="4" t="n">
-        <v>2256</v>
+        <v>2112</v>
       </c>
       <c r="F101" s="3" t="inlineStr">
         <is>
@@ -7437,14 +7433,14 @@
       </c>
       <c r="G101" s="3" t="inlineStr">
         <is>
-          <t>2023-03-21</t>
+          <t>2025-09-02</t>
         </is>
       </c>
       <c r="H101" s="5" t="n">
-        <v>152800000</v>
+        <v>144000000</v>
       </c>
       <c r="I101" s="5" t="n">
-        <v>67730</v>
+        <v>68182</v>
       </c>
       <c r="J101" s="3" t="inlineStr">
         <is>
@@ -7480,12 +7476,12 @@
       </c>
       <c r="B102" s="3" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>9</t>
         </is>
       </c>
       <c r="C102" s="3" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="D102" s="3" t="inlineStr">
@@ -7494,23 +7490,27 @@
         </is>
       </c>
       <c r="E102" s="4" t="n">
-        <v>2112</v>
+        <v>2316</v>
       </c>
       <c r="F102" s="3" t="inlineStr">
         <is>
-          <t>已售</t>
+          <t>待售</t>
         </is>
       </c>
       <c r="G102" s="3" t="inlineStr">
         <is>
-          <t>2025-09-02</t>
-        </is>
-      </c>
-      <c r="H102" s="5" t="n">
-        <v>144000000</v>
-      </c>
-      <c r="I102" s="5" t="n">
-        <v>68182</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H102" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="I102" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
       </c>
       <c r="J102" s="3" t="inlineStr">
         <is>
@@ -7551,7 +7551,7 @@
       </c>
       <c r="C103" s="3" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>6</t>
         </is>
       </c>
       <c r="D103" s="3" t="inlineStr">
@@ -7560,27 +7560,23 @@
         </is>
       </c>
       <c r="E103" s="4" t="n">
-        <v>2316</v>
+        <v>2112</v>
       </c>
       <c r="F103" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>已售</t>
         </is>
       </c>
       <c r="G103" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H103" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="I103" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+          <t>2023-12-12</t>
+        </is>
+      </c>
+      <c r="H103" s="5" t="n">
+        <v>136000000</v>
+      </c>
+      <c r="I103" s="5" t="n">
+        <v>64394</v>
       </c>
       <c r="J103" s="3" t="inlineStr">
         <is>
@@ -7616,12 +7612,12 @@
       </c>
       <c r="B104" s="3" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>8</t>
         </is>
       </c>
       <c r="C104" s="3" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="D104" s="3" t="inlineStr">
@@ -7630,7 +7626,7 @@
         </is>
       </c>
       <c r="E104" s="4" t="n">
-        <v>2112</v>
+        <v>2256</v>
       </c>
       <c r="F104" s="3" t="inlineStr">
         <is>
@@ -7639,14 +7635,14 @@
       </c>
       <c r="G104" s="3" t="inlineStr">
         <is>
-          <t>2023-12-12</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="H104" s="5" t="n">
-        <v>136000000</v>
+        <v>147600000</v>
       </c>
       <c r="I104" s="5" t="n">
-        <v>64394</v>
+        <v>65426</v>
       </c>
       <c r="J104" s="3" t="inlineStr">
         <is>
@@ -7687,7 +7683,7 @@
       </c>
       <c r="C105" s="3" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>6</t>
         </is>
       </c>
       <c r="D105" s="3" t="inlineStr">
@@ -7696,23 +7692,27 @@
         </is>
       </c>
       <c r="E105" s="4" t="n">
-        <v>2256</v>
+        <v>2169</v>
       </c>
       <c r="F105" s="3" t="inlineStr">
         <is>
-          <t>已售</t>
+          <t>待售</t>
         </is>
       </c>
       <c r="G105" s="3" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
-        </is>
-      </c>
-      <c r="H105" s="5" t="n">
-        <v>147600000</v>
-      </c>
-      <c r="I105" s="5" t="n">
-        <v>65426</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H105" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="I105" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
       </c>
       <c r="J105" s="3" t="inlineStr">
         <is>
@@ -7748,12 +7748,12 @@
       </c>
       <c r="B106" s="3" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7</t>
         </is>
       </c>
       <c r="C106" s="3" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="D106" s="3" t="inlineStr">
@@ -7762,27 +7762,23 @@
         </is>
       </c>
       <c r="E106" s="4" t="n">
-        <v>2169</v>
+        <v>2256</v>
       </c>
       <c r="F106" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>已售</t>
         </is>
       </c>
       <c r="G106" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H106" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="I106" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+          <t>2026-07-06</t>
+        </is>
+      </c>
+      <c r="H106" s="5" t="n">
+        <v>144200000</v>
+      </c>
+      <c r="I106" s="5" t="n">
+        <v>63918</v>
       </c>
       <c r="J106" s="3" t="inlineStr">
         <is>
@@ -7823,7 +7819,7 @@
       </c>
       <c r="C107" s="3" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>6</t>
         </is>
       </c>
       <c r="D107" s="3" t="inlineStr">
@@ -7832,7 +7828,7 @@
         </is>
       </c>
       <c r="E107" s="4" t="n">
-        <v>2256</v>
+        <v>2112</v>
       </c>
       <c r="F107" s="3" t="inlineStr">
         <is>
@@ -7845,10 +7841,10 @@
         </is>
       </c>
       <c r="H107" s="5" t="n">
-        <v>144200000</v>
+        <v>130800000</v>
       </c>
       <c r="I107" s="5" t="n">
-        <v>63918</v>
+        <v>61932</v>
       </c>
       <c r="J107" s="3" t="inlineStr">
         <is>
@@ -7884,37 +7880,41 @@
       </c>
       <c r="B108" s="3" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="C108" s="3" t="inlineStr">
+        <is>
           <t>7</t>
         </is>
       </c>
-      <c r="C108" s="3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
       <c r="D108" s="3" t="inlineStr">
         <is>
           <t>4+房</t>
         </is>
       </c>
       <c r="E108" s="4" t="n">
-        <v>2112</v>
+        <v>2316</v>
       </c>
       <c r="F108" s="3" t="inlineStr">
         <is>
-          <t>已售</t>
+          <t>待售</t>
         </is>
       </c>
       <c r="G108" s="3" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
-        </is>
-      </c>
-      <c r="H108" s="5" t="n">
-        <v>130800000</v>
-      </c>
-      <c r="I108" s="5" t="n">
-        <v>61932</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H108" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="I108" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
       </c>
       <c r="J108" s="3" t="inlineStr">
         <is>
@@ -7955,7 +7955,7 @@
       </c>
       <c r="C109" s="3" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>6</t>
         </is>
       </c>
       <c r="D109" s="3" t="inlineStr">
@@ -7964,7 +7964,7 @@
         </is>
       </c>
       <c r="E109" s="4" t="n">
-        <v>2316</v>
+        <v>2169</v>
       </c>
       <c r="F109" s="3" t="inlineStr">
         <is>
@@ -8020,12 +8020,12 @@
       </c>
       <c r="B110" s="3" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>5</t>
         </is>
       </c>
       <c r="C110" s="3" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="D110" s="3" t="inlineStr">
@@ -8034,27 +8034,23 @@
         </is>
       </c>
       <c r="E110" s="4" t="n">
-        <v>2169</v>
+        <v>2256</v>
       </c>
       <c r="F110" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>已售</t>
         </is>
       </c>
       <c r="G110" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H110" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="I110" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+          <t>2026-01-26</t>
+        </is>
+      </c>
+      <c r="H110" s="5" t="n">
+        <v>138421100</v>
+      </c>
+      <c r="I110" s="5" t="n">
+        <v>61357</v>
       </c>
       <c r="J110" s="3" t="inlineStr">
         <is>
@@ -8095,7 +8091,7 @@
       </c>
       <c r="C111" s="3" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>6</t>
         </is>
       </c>
       <c r="D111" s="3" t="inlineStr">
@@ -8104,7 +8100,7 @@
         </is>
       </c>
       <c r="E111" s="4" t="n">
-        <v>2256</v>
+        <v>2112</v>
       </c>
       <c r="F111" s="3" t="inlineStr">
         <is>
@@ -8113,14 +8109,14 @@
       </c>
       <c r="G111" s="3" t="inlineStr">
         <is>
-          <t>2026-01-26</t>
+          <t>2024-07-12</t>
         </is>
       </c>
       <c r="H111" s="5" t="n">
-        <v>138421100</v>
+        <v>117000000</v>
       </c>
       <c r="I111" s="5" t="n">
-        <v>61357</v>
+        <v>55398</v>
       </c>
       <c r="J111" s="3" t="inlineStr">
         <is>
@@ -8156,12 +8152,12 @@
       </c>
       <c r="B112" s="3" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="C112" s="3" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="D112" s="3" t="inlineStr">
@@ -8170,23 +8166,27 @@
         </is>
       </c>
       <c r="E112" s="4" t="n">
-        <v>2112</v>
+        <v>2316</v>
       </c>
       <c r="F112" s="3" t="inlineStr">
         <is>
-          <t>已售</t>
+          <t>待售</t>
         </is>
       </c>
       <c r="G112" s="3" t="inlineStr">
         <is>
-          <t>2024-07-12</t>
-        </is>
-      </c>
-      <c r="H112" s="5" t="n">
-        <v>117000000</v>
-      </c>
-      <c r="I112" s="5" t="n">
-        <v>55398</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H112" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="I112" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
       </c>
       <c r="J112" s="3" t="inlineStr">
         <is>
@@ -8227,7 +8227,7 @@
       </c>
       <c r="C113" s="3" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>6</t>
         </is>
       </c>
       <c r="D113" s="3" t="inlineStr">
@@ -8236,27 +8236,23 @@
         </is>
       </c>
       <c r="E113" s="4" t="n">
-        <v>2316</v>
+        <v>2112</v>
       </c>
       <c r="F113" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>已售</t>
         </is>
       </c>
       <c r="G113" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H113" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="I113" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+          <t>2024-06-12</t>
+        </is>
+      </c>
+      <c r="H113" s="5" t="n">
+        <v>115000000</v>
+      </c>
+      <c r="I113" s="5" t="n">
+        <v>54451</v>
       </c>
       <c r="J113" s="3" t="inlineStr">
         <is>
@@ -8292,12 +8288,12 @@
       </c>
       <c r="B114" s="3" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="C114" s="3" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="D114" s="3" t="inlineStr">
@@ -8306,23 +8302,27 @@
         </is>
       </c>
       <c r="E114" s="4" t="n">
-        <v>2112</v>
+        <v>2316</v>
       </c>
       <c r="F114" s="3" t="inlineStr">
         <is>
-          <t>已售</t>
+          <t>待售</t>
         </is>
       </c>
       <c r="G114" s="3" t="inlineStr">
         <is>
-          <t>2024-06-12</t>
-        </is>
-      </c>
-      <c r="H114" s="5" t="n">
-        <v>115000000</v>
-      </c>
-      <c r="I114" s="5" t="n">
-        <v>54451</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H114" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="I114" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
       </c>
       <c r="J114" s="3" t="inlineStr">
         <is>
@@ -8363,7 +8363,7 @@
       </c>
       <c r="C115" s="3" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>6</t>
         </is>
       </c>
       <c r="D115" s="3" t="inlineStr">
@@ -8372,7 +8372,7 @@
         </is>
       </c>
       <c r="E115" s="4" t="n">
-        <v>2316</v>
+        <v>2169</v>
       </c>
       <c r="F115" s="3" t="inlineStr">
         <is>
@@ -8428,12 +8428,12 @@
       </c>
       <c r="B116" s="3" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="C116" s="3" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="D116" s="3" t="inlineStr">
@@ -8442,27 +8442,23 @@
         </is>
       </c>
       <c r="E116" s="4" t="n">
-        <v>2169</v>
+        <v>2176</v>
       </c>
       <c r="F116" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>已售</t>
         </is>
       </c>
       <c r="G116" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H116" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="I116" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+          <t>2021-10-22</t>
+        </is>
+      </c>
+      <c r="H116" s="5" t="n">
+        <v>154300000</v>
+      </c>
+      <c r="I116" s="5" t="n">
+        <v>70910</v>
       </c>
       <c r="J116" s="3" t="inlineStr">
         <is>
@@ -8503,7 +8499,7 @@
       </c>
       <c r="C117" s="3" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>6</t>
         </is>
       </c>
       <c r="D117" s="3" t="inlineStr">
@@ -8512,7 +8508,7 @@
         </is>
       </c>
       <c r="E117" s="4" t="n">
-        <v>2176</v>
+        <v>2032</v>
       </c>
       <c r="F117" s="3" t="inlineStr">
         <is>
@@ -8521,14 +8517,14 @@
       </c>
       <c r="G117" s="3" t="inlineStr">
         <is>
-          <t>2021-10-22</t>
+          <t>2025-03-14</t>
         </is>
       </c>
       <c r="H117" s="5" t="n">
-        <v>154300000</v>
+        <v>126300000</v>
       </c>
       <c r="I117" s="5" t="n">
-        <v>70910</v>
+        <v>62156</v>
       </c>
       <c r="J117" s="3" t="inlineStr">
         <is>
@@ -8551,72 +8547,6 @@
         </is>
       </c>
       <c r="N117" s="3" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-    </row>
-    <row r="118">
-      <c r="A118" s="3" t="inlineStr">
-        <is>
-          <t>6号及7号</t>
-        </is>
-      </c>
-      <c r="B118" s="3" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="C118" s="3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="D118" s="3" t="inlineStr">
-        <is>
-          <t>4+房</t>
-        </is>
-      </c>
-      <c r="E118" s="4" t="n">
-        <v>2032</v>
-      </c>
-      <c r="F118" s="3" t="inlineStr">
-        <is>
-          <t>已售</t>
-        </is>
-      </c>
-      <c r="G118" s="3" t="inlineStr">
-        <is>
-          <t>2025-03-14</t>
-        </is>
-      </c>
-      <c r="H118" s="5" t="n">
-        <v>126300000</v>
-      </c>
-      <c r="I118" s="5" t="n">
-        <v>62156</v>
-      </c>
-      <c r="J118" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K118" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="L118" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="M118" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N118" s="3" t="inlineStr">
         <is>
           <t>否</t>
         </is>
@@ -8687,7 +8617,7 @@
     <row r="3" ht="20" customHeight="1">
       <c r="A3" s="13" t="inlineStr">
         <is>
-          <t>38</t>
+          <t>37</t>
         </is>
       </c>
       <c r="B3" s="14" t="inlineStr">
@@ -8702,7 +8632,7 @@
       </c>
       <c r="D3" s="16" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>18</t>
         </is>
       </c>
       <c r="E3" s="17" t="inlineStr">

--- a/web/files/港岛-半山区西部-21 Borrett Road 第1期.xlsx
+++ b/web/files/港岛-半山区西部-21 Borrett Road 第1期.xlsx
@@ -22,7 +22,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="$#,##0"/>
   </numFmts>
-  <fonts count="19">
+  <fonts count="20">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -126,6 +126,12 @@
       <color rgb="007F7F7F"/>
       <sz val="8"/>
     </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <b val="1"/>
+      <color rgb="00004D00"/>
+      <sz val="8"/>
+    </font>
   </fonts>
   <fills count="9">
     <fill>
@@ -203,7 +209,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="23">
+  <cellXfs count="24">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -269,6 +275,9 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="18" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -4164,7 +4173,7 @@
       </c>
       <c r="F53" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G53" s="3" t="inlineStr">
@@ -4174,12 +4183,12 @@
       </c>
       <c r="H53" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="I53" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="J53" s="3" t="inlineStr">
@@ -4189,12 +4198,12 @@
       </c>
       <c r="K53" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="L53" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="M53" s="3" t="inlineStr">
@@ -4204,7 +4213,7 @@
       </c>
       <c r="N53" s="3" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
     </row>
@@ -9163,27 +9172,27 @@
       </c>
       <c r="B3" s="14" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C3" s="15" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="C3" s="15" t="inlineStr">
+      <c r="D3" s="16" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="E3" s="17" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="D3" s="16" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
-      <c r="E3" s="17" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="F3" s="18" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>25</t>
         </is>
       </c>
     </row>
@@ -9372,12 +9381,12 @@
 (25年-08月-21日)</t>
         </is>
       </c>
-      <c r="C12" s="22" t="inlineStr">
+      <c r="C12" s="23" t="inlineStr">
         <is>
           <t>5 | 2166呎 (4+房)
--
--
-(待售)</t>
+招标单位
+-
+(在售)</t>
         </is>
       </c>
     </row>

--- a/web/files/港岛-半山区西部-21 Borrett Road 第1期.xlsx
+++ b/web/files/港岛-半山区西部-21 Borrett Road 第1期.xlsx
@@ -765,7 +765,7 @@
         </is>
       </c>
       <c r="E3" s="4" t="n">
-        <v>3309</v>
+        <v>3378</v>
       </c>
       <c r="F3" s="3" t="inlineStr">
         <is>
@@ -781,7 +781,7 @@
         <v>459408000</v>
       </c>
       <c r="I3" s="5" t="n">
-        <v>138836</v>
+        <v>136000</v>
       </c>
       <c r="J3" s="3" t="inlineStr">
         <is>
@@ -1111,7 +1111,7 @@
         </is>
       </c>
       <c r="E8" s="4" t="n">
-        <v>2096</v>
+        <v>2154</v>
       </c>
       <c r="F8" s="3" t="inlineStr">
         <is>
@@ -1127,7 +1127,7 @@
         <v>180800000</v>
       </c>
       <c r="I8" s="5" t="n">
-        <v>86260</v>
+        <v>83937</v>
       </c>
       <c r="J8" s="3" t="inlineStr">
         <is>
@@ -1177,7 +1177,7 @@
         </is>
       </c>
       <c r="E9" s="4" t="n">
-        <v>2886</v>
+        <v>2945</v>
       </c>
       <c r="F9" s="3" t="inlineStr">
         <is>
@@ -1193,7 +1193,7 @@
         <v>270633660</v>
       </c>
       <c r="I9" s="5" t="n">
-        <v>93775</v>
+        <v>91896</v>
       </c>
       <c r="J9" s="3" t="inlineStr">
         <is>
@@ -1243,7 +1243,7 @@
         </is>
       </c>
       <c r="E10" s="4" t="n">
-        <v>2096</v>
+        <v>2154</v>
       </c>
       <c r="F10" s="3" t="inlineStr">
         <is>
@@ -1259,7 +1259,7 @@
         <v>169520000</v>
       </c>
       <c r="I10" s="5" t="n">
-        <v>80878</v>
+        <v>78700</v>
       </c>
       <c r="J10" s="3" t="inlineStr">
         <is>
@@ -1309,7 +1309,7 @@
         </is>
       </c>
       <c r="E11" s="4" t="n">
-        <v>2886</v>
+        <v>2945</v>
       </c>
       <c r="F11" s="3" t="inlineStr">
         <is>
@@ -1325,7 +1325,7 @@
         <v>250000000</v>
       </c>
       <c r="I11" s="5" t="n">
-        <v>86625</v>
+        <v>84890</v>
       </c>
       <c r="J11" s="3" t="inlineStr">
         <is>
@@ -1375,7 +1375,7 @@
         </is>
       </c>
       <c r="E12" s="4" t="n">
-        <v>2096</v>
+        <v>2154</v>
       </c>
       <c r="F12" s="3" t="inlineStr">
         <is>
@@ -1391,7 +1391,7 @@
         <v>170000000</v>
       </c>
       <c r="I12" s="5" t="n">
-        <v>81107</v>
+        <v>78923</v>
       </c>
       <c r="J12" s="3" t="inlineStr">
         <is>
@@ -1511,7 +1511,7 @@
         </is>
       </c>
       <c r="E14" s="4" t="n">
-        <v>2096</v>
+        <v>2154</v>
       </c>
       <c r="F14" s="3" t="inlineStr">
         <is>
@@ -1527,7 +1527,7 @@
         <v>160000000</v>
       </c>
       <c r="I14" s="5" t="n">
-        <v>76336</v>
+        <v>74280</v>
       </c>
       <c r="J14" s="3" t="inlineStr">
         <is>
@@ -1643,7 +1643,7 @@
         </is>
       </c>
       <c r="E16" s="4" t="n">
-        <v>2096</v>
+        <v>2154</v>
       </c>
       <c r="F16" s="3" t="inlineStr">
         <is>
@@ -1659,7 +1659,7 @@
         <v>155000000</v>
       </c>
       <c r="I16" s="5" t="n">
-        <v>73950</v>
+        <v>71959</v>
       </c>
       <c r="J16" s="3" t="inlineStr">
         <is>
@@ -1709,7 +1709,7 @@
         </is>
       </c>
       <c r="E17" s="4" t="n">
-        <v>2886</v>
+        <v>2945</v>
       </c>
       <c r="F17" s="3" t="inlineStr">
         <is>
@@ -1725,7 +1725,7 @@
         <v>232800000</v>
       </c>
       <c r="I17" s="5" t="n">
-        <v>80665</v>
+        <v>79049</v>
       </c>
       <c r="J17" s="3" t="inlineStr">
         <is>
@@ -1841,7 +1841,7 @@
         </is>
       </c>
       <c r="E19" s="4" t="n">
-        <v>2886</v>
+        <v>2945</v>
       </c>
       <c r="F19" s="3" t="inlineStr">
         <is>
@@ -1857,7 +1857,7 @@
         <v>231460000</v>
       </c>
       <c r="I19" s="5" t="n">
-        <v>80201</v>
+        <v>78594</v>
       </c>
       <c r="J19" s="3" t="inlineStr">
         <is>
@@ -1907,7 +1907,7 @@
         </is>
       </c>
       <c r="E20" s="4" t="n">
-        <v>2096</v>
+        <v>2154</v>
       </c>
       <c r="F20" s="3" t="inlineStr">
         <is>
@@ -1923,7 +1923,7 @@
         <v>145500000</v>
       </c>
       <c r="I20" s="5" t="n">
-        <v>69418</v>
+        <v>67549</v>
       </c>
       <c r="J20" s="3" t="inlineStr">
         <is>
@@ -1973,7 +1973,7 @@
         </is>
       </c>
       <c r="E21" s="4" t="n">
-        <v>2886</v>
+        <v>2945</v>
       </c>
       <c r="F21" s="3" t="inlineStr">
         <is>
@@ -1989,7 +1989,7 @@
         <v>229710000</v>
       </c>
       <c r="I21" s="5" t="n">
-        <v>79595</v>
+        <v>78000</v>
       </c>
       <c r="J21" s="3" t="inlineStr">
         <is>
@@ -2039,7 +2039,7 @@
         </is>
       </c>
       <c r="E22" s="4" t="n">
-        <v>2096</v>
+        <v>2154</v>
       </c>
       <c r="F22" s="3" t="inlineStr">
         <is>
@@ -2055,7 +2055,7 @@
         <v>136000000</v>
       </c>
       <c r="I22" s="5" t="n">
-        <v>64885</v>
+        <v>63138</v>
       </c>
       <c r="J22" s="3" t="inlineStr">
         <is>
@@ -2105,7 +2105,7 @@
         </is>
       </c>
       <c r="E23" s="4" t="n">
-        <v>2886</v>
+        <v>2945</v>
       </c>
       <c r="F23" s="3" t="inlineStr">
         <is>
@@ -2121,7 +2121,7 @@
         <v>210347500</v>
       </c>
       <c r="I23" s="5" t="n">
-        <v>72885</v>
+        <v>71425</v>
       </c>
       <c r="J23" s="3" t="inlineStr">
         <is>
@@ -2237,7 +2237,7 @@
         </is>
       </c>
       <c r="E25" s="4" t="n">
-        <v>2886</v>
+        <v>2945</v>
       </c>
       <c r="F25" s="3" t="inlineStr">
         <is>
@@ -2253,7 +2253,7 @@
         <v>218000000</v>
       </c>
       <c r="I25" s="5" t="n">
-        <v>75537</v>
+        <v>74024</v>
       </c>
       <c r="J25" s="3" t="inlineStr">
         <is>
@@ -3283,7 +3283,7 @@
         </is>
       </c>
       <c r="E40" s="4" t="n">
-        <v>2664</v>
+        <v>2731</v>
       </c>
       <c r="F40" s="3" t="inlineStr">
         <is>
@@ -3299,7 +3299,7 @@
         <v>344106000</v>
       </c>
       <c r="I40" s="5" t="n">
-        <v>129169</v>
+        <v>126000</v>
       </c>
       <c r="J40" s="3" t="inlineStr">
         <is>
@@ -3349,7 +3349,7 @@
         </is>
       </c>
       <c r="E41" s="4" t="n">
-        <v>2109</v>
+        <v>2166</v>
       </c>
       <c r="F41" s="3" t="inlineStr">
         <is>
@@ -3365,7 +3365,7 @@
         <v>186000000</v>
       </c>
       <c r="I41" s="5" t="n">
-        <v>88193</v>
+        <v>85873</v>
       </c>
       <c r="J41" s="3" t="inlineStr">
         <is>
@@ -3415,7 +3415,7 @@
         </is>
       </c>
       <c r="E42" s="4" t="n">
-        <v>2133</v>
+        <v>2193</v>
       </c>
       <c r="F42" s="3" t="inlineStr">
         <is>
@@ -3431,7 +3431,7 @@
         <v>200000000</v>
       </c>
       <c r="I42" s="5" t="n">
-        <v>93765</v>
+        <v>91199</v>
       </c>
       <c r="J42" s="3" t="inlineStr">
         <is>
@@ -3831,7 +3831,7 @@
         </is>
       </c>
       <c r="E48" s="4" t="n">
-        <v>2133</v>
+        <v>2193</v>
       </c>
       <c r="F48" s="3" t="inlineStr">
         <is>
@@ -3847,7 +3847,7 @@
         <v>176800000</v>
       </c>
       <c r="I48" s="5" t="n">
-        <v>82888</v>
+        <v>80620</v>
       </c>
       <c r="J48" s="3" t="inlineStr">
         <is>
@@ -3967,7 +3967,7 @@
         </is>
       </c>
       <c r="E50" s="4" t="n">
-        <v>2133</v>
+        <v>2193</v>
       </c>
       <c r="F50" s="3" t="inlineStr">
         <is>
@@ -3983,7 +3983,7 @@
         <v>172000000</v>
       </c>
       <c r="I50" s="5" t="n">
-        <v>80638</v>
+        <v>78431</v>
       </c>
       <c r="J50" s="3" t="inlineStr">
         <is>
@@ -4103,7 +4103,7 @@
         </is>
       </c>
       <c r="E52" s="4" t="n">
-        <v>2133</v>
+        <v>2193</v>
       </c>
       <c r="F52" s="3" t="inlineStr">
         <is>
@@ -4119,7 +4119,7 @@
         <v>167800000</v>
       </c>
       <c r="I52" s="5" t="n">
-        <v>78669</v>
+        <v>76516</v>
       </c>
       <c r="J52" s="3" t="inlineStr">
         <is>
@@ -4239,7 +4239,7 @@
         </is>
       </c>
       <c r="E54" s="4" t="n">
-        <v>2133</v>
+        <v>2193</v>
       </c>
       <c r="F54" s="3" t="inlineStr">
         <is>
@@ -4255,7 +4255,7 @@
         <v>162000000</v>
       </c>
       <c r="I54" s="5" t="n">
-        <v>75949</v>
+        <v>73871</v>
       </c>
       <c r="J54" s="3" t="inlineStr">
         <is>
@@ -4375,7 +4375,7 @@
         </is>
       </c>
       <c r="E56" s="4" t="n">
-        <v>2133</v>
+        <v>2193</v>
       </c>
       <c r="F56" s="3" t="inlineStr">
         <is>
@@ -4391,7 +4391,7 @@
         <v>156000000</v>
       </c>
       <c r="I56" s="5" t="n">
-        <v>73136</v>
+        <v>71135</v>
       </c>
       <c r="J56" s="3" t="inlineStr">
         <is>
@@ -4511,7 +4511,7 @@
         </is>
       </c>
       <c r="E58" s="4" t="n">
-        <v>2133</v>
+        <v>2193</v>
       </c>
       <c r="F58" s="3" t="inlineStr">
         <is>
@@ -4527,7 +4527,7 @@
         <v>153800000</v>
       </c>
       <c r="I58" s="5" t="n">
-        <v>72105</v>
+        <v>70132</v>
       </c>
       <c r="J58" s="3" t="inlineStr">
         <is>
@@ -4647,7 +4647,7 @@
         </is>
       </c>
       <c r="E60" s="4" t="n">
-        <v>2133</v>
+        <v>2193</v>
       </c>
       <c r="F60" s="3" t="inlineStr">
         <is>
@@ -4663,7 +4663,7 @@
         <v>151000000</v>
       </c>
       <c r="I60" s="5" t="n">
-        <v>70792</v>
+        <v>68855</v>
       </c>
       <c r="J60" s="3" t="inlineStr">
         <is>
@@ -4783,7 +4783,7 @@
         </is>
       </c>
       <c r="E62" s="4" t="n">
-        <v>2133</v>
+        <v>2193</v>
       </c>
       <c r="F62" s="3" t="inlineStr">
         <is>
@@ -4799,7 +4799,7 @@
         <v>148000000</v>
       </c>
       <c r="I62" s="5" t="n">
-        <v>69386</v>
+        <v>67487</v>
       </c>
       <c r="J62" s="3" t="inlineStr">
         <is>
@@ -5829,7 +5829,7 @@
         </is>
       </c>
       <c r="E77" s="4" t="n">
-        <v>2029</v>
+        <v>2086</v>
       </c>
       <c r="F77" s="3" t="inlineStr">
         <is>
@@ -5845,7 +5845,7 @@
         <v>125600000</v>
       </c>
       <c r="I77" s="5" t="n">
-        <v>61902</v>
+        <v>60211</v>
       </c>
       <c r="J77" s="3" t="inlineStr">
         <is>
@@ -5895,7 +5895,7 @@
         </is>
       </c>
       <c r="E78" s="4" t="n">
-        <v>2065</v>
+        <v>2112</v>
       </c>
       <c r="F78" s="3" t="inlineStr">
         <is>
@@ -5911,7 +5911,7 @@
         <v>126950000</v>
       </c>
       <c r="I78" s="5" t="n">
-        <v>61477</v>
+        <v>60109</v>
       </c>
       <c r="J78" s="3" t="inlineStr">
         <is>
@@ -5961,7 +5961,7 @@
         </is>
       </c>
       <c r="E79" s="4" t="n">
-        <v>2927</v>
+        <v>2995</v>
       </c>
       <c r="F79" s="3" t="inlineStr">
         <is>
@@ -5977,7 +5977,7 @@
         <v>377370000</v>
       </c>
       <c r="I79" s="5" t="n">
-        <v>128927</v>
+        <v>126000</v>
       </c>
       <c r="J79" s="3" t="inlineStr">
         <is>
@@ -6027,7 +6027,7 @@
         </is>
       </c>
       <c r="E80" s="4" t="n">
-        <v>2256</v>
+        <v>2316</v>
       </c>
       <c r="F80" s="3" t="inlineStr">
         <is>
@@ -6043,7 +6043,7 @@
         <v>208500000</v>
       </c>
       <c r="I80" s="5" t="n">
-        <v>92420</v>
+        <v>90026</v>
       </c>
       <c r="J80" s="3" t="inlineStr">
         <is>
@@ -6093,7 +6093,7 @@
         </is>
       </c>
       <c r="E81" s="4" t="n">
-        <v>2112</v>
+        <v>2169</v>
       </c>
       <c r="F81" s="3" t="inlineStr">
         <is>
@@ -6109,7 +6109,7 @@
         <v>181500000</v>
       </c>
       <c r="I81" s="5" t="n">
-        <v>85938</v>
+        <v>83679</v>
       </c>
       <c r="J81" s="3" t="inlineStr">
         <is>
@@ -6159,7 +6159,7 @@
         </is>
       </c>
       <c r="E82" s="4" t="n">
-        <v>2256</v>
+        <v>2316</v>
       </c>
       <c r="F82" s="3" t="inlineStr">
         <is>
@@ -6175,7 +6175,7 @@
         <v>203888000</v>
       </c>
       <c r="I82" s="5" t="n">
-        <v>90376</v>
+        <v>88035</v>
       </c>
       <c r="J82" s="3" t="inlineStr">
         <is>
@@ -6225,7 +6225,7 @@
         </is>
       </c>
       <c r="E83" s="4" t="n">
-        <v>2112</v>
+        <v>2169</v>
       </c>
       <c r="F83" s="3" t="inlineStr">
         <is>
@@ -6241,7 +6241,7 @@
         <v>190110000</v>
       </c>
       <c r="I83" s="5" t="n">
-        <v>90014</v>
+        <v>87649</v>
       </c>
       <c r="J83" s="3" t="inlineStr">
         <is>
@@ -6431,7 +6431,7 @@
         </is>
       </c>
       <c r="E86" s="4" t="n">
-        <v>2256</v>
+        <v>2316</v>
       </c>
       <c r="F86" s="3" t="inlineStr">
         <is>
@@ -6447,7 +6447,7 @@
         <v>190380000</v>
       </c>
       <c r="I86" s="5" t="n">
-        <v>84388</v>
+        <v>82202</v>
       </c>
       <c r="J86" s="3" t="inlineStr">
         <is>
@@ -6497,7 +6497,7 @@
         </is>
       </c>
       <c r="E87" s="4" t="n">
-        <v>2112</v>
+        <v>2169</v>
       </c>
       <c r="F87" s="3" t="inlineStr">
         <is>
@@ -6513,7 +6513,7 @@
         <v>172000000</v>
       </c>
       <c r="I87" s="5" t="n">
-        <v>81439</v>
+        <v>79299</v>
       </c>
       <c r="J87" s="3" t="inlineStr">
         <is>
@@ -6563,7 +6563,7 @@
         </is>
       </c>
       <c r="E88" s="4" t="n">
-        <v>2256</v>
+        <v>2316</v>
       </c>
       <c r="F88" s="3" t="inlineStr">
         <is>
@@ -6579,7 +6579,7 @@
         <v>185233680</v>
       </c>
       <c r="I88" s="5" t="n">
-        <v>82107</v>
+        <v>79980</v>
       </c>
       <c r="J88" s="3" t="inlineStr">
         <is>
@@ -6629,7 +6629,7 @@
         </is>
       </c>
       <c r="E89" s="4" t="n">
-        <v>2112</v>
+        <v>2169</v>
       </c>
       <c r="F89" s="3" t="inlineStr">
         <is>
@@ -6645,7 +6645,7 @@
         <v>166800000</v>
       </c>
       <c r="I89" s="5" t="n">
-        <v>78977</v>
+        <v>76902</v>
       </c>
       <c r="J89" s="3" t="inlineStr">
         <is>
@@ -6695,7 +6695,7 @@
         </is>
       </c>
       <c r="E90" s="4" t="n">
-        <v>2256</v>
+        <v>2316</v>
       </c>
       <c r="F90" s="3" t="inlineStr">
         <is>
@@ -6711,7 +6711,7 @@
         <v>180000000</v>
       </c>
       <c r="I90" s="5" t="n">
-        <v>79787</v>
+        <v>77720</v>
       </c>
       <c r="J90" s="3" t="inlineStr">
         <is>
@@ -6831,7 +6831,7 @@
         </is>
       </c>
       <c r="E92" s="4" t="n">
-        <v>2256</v>
+        <v>2316</v>
       </c>
       <c r="F92" s="3" t="inlineStr">
         <is>
@@ -6847,7 +6847,7 @@
         <v>173600000</v>
       </c>
       <c r="I92" s="5" t="n">
-        <v>76950</v>
+        <v>74957</v>
       </c>
       <c r="J92" s="3" t="inlineStr">
         <is>
@@ -6897,7 +6897,7 @@
         </is>
       </c>
       <c r="E93" s="4" t="n">
-        <v>2112</v>
+        <v>2169</v>
       </c>
       <c r="F93" s="3" t="inlineStr">
         <is>
@@ -6913,7 +6913,7 @@
         <v>159300000</v>
       </c>
       <c r="I93" s="5" t="n">
-        <v>75426</v>
+        <v>73444</v>
       </c>
       <c r="J93" s="3" t="inlineStr">
         <is>
@@ -6963,7 +6963,7 @@
         </is>
       </c>
       <c r="E94" s="4" t="n">
-        <v>2256</v>
+        <v>2316</v>
       </c>
       <c r="F94" s="3" t="inlineStr">
         <is>
@@ -6979,7 +6979,7 @@
         <v>168000000</v>
       </c>
       <c r="I94" s="5" t="n">
-        <v>74468</v>
+        <v>72539</v>
       </c>
       <c r="J94" s="3" t="inlineStr">
         <is>
@@ -7029,7 +7029,7 @@
         </is>
       </c>
       <c r="E95" s="4" t="n">
-        <v>2112</v>
+        <v>2169</v>
       </c>
       <c r="F95" s="3" t="inlineStr">
         <is>
@@ -7045,7 +7045,7 @@
         <v>154800000</v>
       </c>
       <c r="I95" s="5" t="n">
-        <v>73295</v>
+        <v>71369</v>
       </c>
       <c r="J95" s="3" t="inlineStr">
         <is>
@@ -7165,7 +7165,7 @@
         </is>
       </c>
       <c r="E97" s="4" t="n">
-        <v>2112</v>
+        <v>2169</v>
       </c>
       <c r="F97" s="3" t="inlineStr">
         <is>
@@ -7181,7 +7181,7 @@
         <v>140000000</v>
       </c>
       <c r="I97" s="5" t="n">
-        <v>66288</v>
+        <v>64546</v>
       </c>
       <c r="J97" s="3" t="inlineStr">
         <is>
@@ -7231,7 +7231,7 @@
         </is>
       </c>
       <c r="E98" s="4" t="n">
-        <v>2256</v>
+        <v>2316</v>
       </c>
       <c r="F98" s="3" t="inlineStr">
         <is>
@@ -7247,7 +7247,7 @@
         <v>162800000</v>
       </c>
       <c r="I98" s="5" t="n">
-        <v>72163</v>
+        <v>70294</v>
       </c>
       <c r="J98" s="3" t="inlineStr">
         <is>
@@ -7367,7 +7367,7 @@
         </is>
       </c>
       <c r="E100" s="4" t="n">
-        <v>2256</v>
+        <v>2316</v>
       </c>
       <c r="F100" s="3" t="inlineStr">
         <is>
@@ -7383,7 +7383,7 @@
         <v>152800000</v>
       </c>
       <c r="I100" s="5" t="n">
-        <v>67730</v>
+        <v>65976</v>
       </c>
       <c r="J100" s="3" t="inlineStr">
         <is>
@@ -7433,7 +7433,7 @@
         </is>
       </c>
       <c r="E101" s="4" t="n">
-        <v>2112</v>
+        <v>2169</v>
       </c>
       <c r="F101" s="3" t="inlineStr">
         <is>
@@ -7449,7 +7449,7 @@
         <v>144000000</v>
       </c>
       <c r="I101" s="5" t="n">
-        <v>68182</v>
+        <v>66390</v>
       </c>
       <c r="J101" s="3" t="inlineStr">
         <is>
@@ -7569,7 +7569,7 @@
         </is>
       </c>
       <c r="E103" s="4" t="n">
-        <v>2112</v>
+        <v>2169</v>
       </c>
       <c r="F103" s="3" t="inlineStr">
         <is>
@@ -7585,7 +7585,7 @@
         <v>136000000</v>
       </c>
       <c r="I103" s="5" t="n">
-        <v>64394</v>
+        <v>62702</v>
       </c>
       <c r="J103" s="3" t="inlineStr">
         <is>
@@ -7635,7 +7635,7 @@
         </is>
       </c>
       <c r="E104" s="4" t="n">
-        <v>2256</v>
+        <v>2316</v>
       </c>
       <c r="F104" s="3" t="inlineStr">
         <is>
@@ -7651,7 +7651,7 @@
         <v>147600000</v>
       </c>
       <c r="I104" s="5" t="n">
-        <v>65426</v>
+        <v>63731</v>
       </c>
       <c r="J104" s="3" t="inlineStr">
         <is>
@@ -7771,7 +7771,7 @@
         </is>
       </c>
       <c r="E106" s="4" t="n">
-        <v>2256</v>
+        <v>2316</v>
       </c>
       <c r="F106" s="3" t="inlineStr">
         <is>
@@ -7787,7 +7787,7 @@
         <v>144200000</v>
       </c>
       <c r="I106" s="5" t="n">
-        <v>63918</v>
+        <v>62263</v>
       </c>
       <c r="J106" s="3" t="inlineStr">
         <is>
@@ -7837,7 +7837,7 @@
         </is>
       </c>
       <c r="E107" s="4" t="n">
-        <v>2112</v>
+        <v>2169</v>
       </c>
       <c r="F107" s="3" t="inlineStr">
         <is>
@@ -7853,7 +7853,7 @@
         <v>130800000</v>
       </c>
       <c r="I107" s="5" t="n">
-        <v>61932</v>
+        <v>60304</v>
       </c>
       <c r="J107" s="3" t="inlineStr">
         <is>
@@ -8043,7 +8043,7 @@
         </is>
       </c>
       <c r="E110" s="4" t="n">
-        <v>2256</v>
+        <v>2316</v>
       </c>
       <c r="F110" s="3" t="inlineStr">
         <is>
@@ -8059,7 +8059,7 @@
         <v>138421100</v>
       </c>
       <c r="I110" s="5" t="n">
-        <v>61357</v>
+        <v>59767</v>
       </c>
       <c r="J110" s="3" t="inlineStr">
         <is>
@@ -8109,7 +8109,7 @@
         </is>
       </c>
       <c r="E111" s="4" t="n">
-        <v>2112</v>
+        <v>2169</v>
       </c>
       <c r="F111" s="3" t="inlineStr">
         <is>
@@ -8125,7 +8125,7 @@
         <v>117000000</v>
       </c>
       <c r="I111" s="5" t="n">
-        <v>55398</v>
+        <v>53942</v>
       </c>
       <c r="J111" s="3" t="inlineStr">
         <is>
@@ -8245,7 +8245,7 @@
         </is>
       </c>
       <c r="E113" s="4" t="n">
-        <v>2112</v>
+        <v>2169</v>
       </c>
       <c r="F113" s="3" t="inlineStr">
         <is>
@@ -8261,7 +8261,7 @@
         <v>115000000</v>
       </c>
       <c r="I113" s="5" t="n">
-        <v>54451</v>
+        <v>53020</v>
       </c>
       <c r="J113" s="3" t="inlineStr">
         <is>
@@ -8451,7 +8451,7 @@
         </is>
       </c>
       <c r="E116" s="4" t="n">
-        <v>2176</v>
+        <v>2236</v>
       </c>
       <c r="F116" s="3" t="inlineStr">
         <is>
@@ -8467,7 +8467,7 @@
         <v>154300000</v>
       </c>
       <c r="I116" s="5" t="n">
-        <v>70910</v>
+        <v>69007</v>
       </c>
       <c r="J116" s="3" t="inlineStr">
         <is>
@@ -8517,7 +8517,7 @@
         </is>
       </c>
       <c r="E117" s="4" t="n">
-        <v>2032</v>
+        <v>2089</v>
       </c>
       <c r="F117" s="3" t="inlineStr">
         <is>
@@ -8533,7 +8533,7 @@
         <v>126300000</v>
       </c>
       <c r="I117" s="5" t="n">
-        <v>62156</v>
+        <v>60460</v>
       </c>
       <c r="J117" s="3" t="inlineStr">
         <is>
@@ -8680,9 +8680,9 @@
       </c>
       <c r="B5" s="20" t="inlineStr">
         <is>
-          <t>1 | 3309呎 (4+房)
+          <t>1 | 3378呎 (4+房)
 $45941万
-$138,836/呎
+$136,000/呎
 (21年-03月-03日)</t>
         </is>
       </c>
@@ -8742,17 +8742,17 @@
       </c>
       <c r="B8" s="20" t="inlineStr">
         <is>
-          <t>1 | 2886呎 (4+房)
+          <t>1 | 2945呎 (4+房)
 $27063万
-$93,775/呎
+$91,896/呎
 (22年-06月-23日)</t>
         </is>
       </c>
       <c r="C8" s="20" t="inlineStr">
         <is>
-          <t>2 | 2096呎 (4+房)
+          <t>2 | 2154呎 (4+房)
 $18080万
-$86,260/呎
+$83,937/呎
 (23年-10月-25日)</t>
         </is>
       </c>
@@ -8765,17 +8765,17 @@
       </c>
       <c r="B9" s="20" t="inlineStr">
         <is>
-          <t>1 | 2886呎 (4+房)
+          <t>1 | 2945呎 (4+房)
 $25000万
-$86,625/呎
+$84,890/呎
 (21年-05月-28日)</t>
         </is>
       </c>
       <c r="C9" s="20" t="inlineStr">
         <is>
-          <t>2 | 2096呎 (4+房)
+          <t>2 | 2154呎 (4+房)
 $16952万
-$80,878/呎
+$78,700/呎
 (21年-07月-16日)</t>
         </is>
       </c>
@@ -8796,9 +8796,9 @@
       </c>
       <c r="C10" s="20" t="inlineStr">
         <is>
-          <t>2 | 2096呎 (4+房)
+          <t>2 | 2154呎 (4+房)
 $17000万
-$81,107/呎
+$78,923/呎
 (21年-05月-28日)</t>
         </is>
       </c>
@@ -8819,9 +8819,9 @@
       </c>
       <c r="C11" s="20" t="inlineStr">
         <is>
-          <t>2 | 2096呎 (4+房)
+          <t>2 | 2154呎 (4+房)
 $16000万
-$76,336/呎
+$74,280/呎
 (21年-09月-30日)</t>
         </is>
       </c>
@@ -8834,17 +8834,17 @@
       </c>
       <c r="B12" s="20" t="inlineStr">
         <is>
-          <t>1 | 2886呎 (4+房)
+          <t>1 | 2945呎 (4+房)
 $23280万
-$80,665/呎
+$79,049/呎
 (21年-06月-02日)</t>
         </is>
       </c>
       <c r="C12" s="20" t="inlineStr">
         <is>
-          <t>2 | 2096呎 (4+房)
+          <t>2 | 2154呎 (4+房)
 $15500万
-$73,950/呎
+$71,959/呎
 (21年-07月-06日)</t>
         </is>
       </c>
@@ -8857,9 +8857,9 @@
       </c>
       <c r="B13" s="20" t="inlineStr">
         <is>
-          <t>1 | 2886呎 (4+房)
+          <t>1 | 2945呎 (4+房)
 $23146万
-$80,201/呎
+$78,594/呎
 (21年-06月-25日)</t>
         </is>
       </c>
@@ -8880,17 +8880,17 @@
       </c>
       <c r="B14" s="20" t="inlineStr">
         <is>
-          <t>1 | 2886呎 (4+房)
+          <t>1 | 2945呎 (4+房)
 $22971万
-$79,595/呎
+$78,000/呎
 (21年-07月-06日)</t>
         </is>
       </c>
       <c r="C14" s="20" t="inlineStr">
         <is>
-          <t>2 | 2096呎 (4+房)
+          <t>2 | 2154呎 (4+房)
 $14550万
-$69,418/呎
+$67,549/呎
 (23年-03月-24日)</t>
         </is>
       </c>
@@ -8903,17 +8903,17 @@
       </c>
       <c r="B15" s="20" t="inlineStr">
         <is>
-          <t>1 | 2886呎 (4+房)
+          <t>1 | 2945呎 (4+房)
 $21035万
-$72,885/呎
+$71,425/呎
 (26年-02月-05日)</t>
         </is>
       </c>
       <c r="C15" s="20" t="inlineStr">
         <is>
-          <t>2 | 2096呎 (4+房)
+          <t>2 | 2154呎 (4+房)
 $13600万
-$64,885/呎
+$63,138/呎
 (24年-11月-29日)</t>
         </is>
       </c>
@@ -8926,9 +8926,9 @@
       </c>
       <c r="B16" s="20" t="inlineStr">
         <is>
-          <t>1 | 2886呎 (4+房)
+          <t>1 | 2945呎 (4+房)
 $21800万
-$75,537/呎
+$74,024/呎
 (24年-04月-29日)</t>
         </is>
       </c>
@@ -9221,9 +9221,9 @@
       </c>
       <c r="B5" s="20" t="inlineStr">
         <is>
-          <t>3 | 2664呎 (4+房)
+          <t>3 | 2731呎 (4+房)
 $34411万
-$129,169/呎
+$126,000/呎
 (21年-05月-11日)</t>
         </is>
       </c>
@@ -9237,17 +9237,17 @@
       </c>
       <c r="B6" s="20" t="inlineStr">
         <is>
-          <t>3 | 2133呎 (4+房)
+          <t>3 | 2193呎 (4+房)
 $20000万
-$93,765/呎
+$91,199/呎
 (21年-11月-24日)</t>
         </is>
       </c>
       <c r="C6" s="20" t="inlineStr">
         <is>
-          <t>5 | 2109呎 (4+房)
+          <t>5 | 2166呎 (4+房)
 $18600万
-$88,193/呎
+$85,873/呎
 (21年-11月-24日)</t>
         </is>
       </c>
@@ -9306,9 +9306,9 @@
       </c>
       <c r="B9" s="20" t="inlineStr">
         <is>
-          <t>3 | 2133呎 (4+房)
+          <t>3 | 2193呎 (4+房)
 $17680万
-$82,888/呎
+$80,620/呎
 (22年-01月-07日)</t>
         </is>
       </c>
@@ -9329,9 +9329,9 @@
       </c>
       <c r="B10" s="20" t="inlineStr">
         <is>
-          <t>3 | 2133呎 (4+房)
+          <t>3 | 2193呎 (4+房)
 $17200万
-$80,638/呎
+$78,431/呎
 (21年-06月-30日)</t>
         </is>
       </c>
@@ -9352,9 +9352,9 @@
       </c>
       <c r="B11" s="20" t="inlineStr">
         <is>
-          <t>3 | 2133呎 (4+房)
+          <t>3 | 2193呎 (4+房)
 $16780万
-$78,669/呎
+$76,516/呎
 (22年-03月-01日)</t>
         </is>
       </c>
@@ -9375,9 +9375,9 @@
       </c>
       <c r="B12" s="20" t="inlineStr">
         <is>
-          <t>3 | 2133呎 (4+房)
+          <t>3 | 2193呎 (4+房)
 $16200万
-$75,949/呎
+$73,871/呎
 (25年-08月-21日)</t>
         </is>
       </c>
@@ -9398,9 +9398,9 @@
       </c>
       <c r="B13" s="20" t="inlineStr">
         <is>
-          <t>3 | 2133呎 (4+房)
+          <t>3 | 2193呎 (4+房)
 $15600万
-$73,136/呎
+$71,135/呎
 (24年-12月-10日)</t>
         </is>
       </c>
@@ -9421,9 +9421,9 @@
       </c>
       <c r="B14" s="20" t="inlineStr">
         <is>
-          <t>3 | 2133呎 (4+房)
+          <t>3 | 2193呎 (4+房)
 $15380万
-$72,105/呎
+$70,132/呎
 (23年-05月-05日)</t>
         </is>
       </c>
@@ -9444,9 +9444,9 @@
       </c>
       <c r="B15" s="20" t="inlineStr">
         <is>
-          <t>3 | 2133呎 (4+房)
+          <t>3 | 2193呎 (4+房)
 $15100万
-$70,792/呎
+$68,855/呎
 (26年-09月-03日)</t>
         </is>
       </c>
@@ -9467,9 +9467,9 @@
       </c>
       <c r="B16" s="20" t="inlineStr">
         <is>
-          <t>3 | 2133呎 (4+房)
+          <t>3 | 2193呎 (4+房)
 $14800万
-$69,386/呎
+$67,487/呎
 (25年-06月-19日)</t>
         </is>
       </c>
@@ -9651,17 +9651,17 @@
       </c>
       <c r="B24" s="20" t="inlineStr">
         <is>
-          <t>3 | 2065呎 (4+房)
+          <t>3 | 2112呎 (4+房)
 $12695万
-$61,477/呎
+$60,109/呎
 (25年-04月-25日)</t>
         </is>
       </c>
       <c r="C24" s="20" t="inlineStr">
         <is>
-          <t>5 | 2029呎 (4+房)
+          <t>5 | 2086呎 (4+房)
 $12560万
-$61,902/呎
+$60,211/呎
 (25年-10月-03日)</t>
         </is>
       </c>
@@ -9785,9 +9785,9 @@
       </c>
       <c r="B5" s="20" t="inlineStr">
         <is>
-          <t>6 | 2927呎 (4+房)
+          <t>6 | 2995呎 (4+房)
 $37737万
-$128,927/呎
+$126,000/呎
 (21年-04月-16日)</t>
         </is>
       </c>
@@ -9801,17 +9801,17 @@
       </c>
       <c r="B6" s="20" t="inlineStr">
         <is>
-          <t>6 | 2112呎 (4+房)
+          <t>6 | 2169呎 (4+房)
 $18150万
-$85,938/呎
+$83,679/呎
 (21年-08月-03日)</t>
         </is>
       </c>
       <c r="C6" s="20" t="inlineStr">
         <is>
-          <t>7 | 2256呎 (4+房)
+          <t>7 | 2316呎 (4+房)
 $20850万
-$92,420/呎
+$90,026/呎
 (21年-08月-03日)</t>
         </is>
       </c>
@@ -9824,17 +9824,17 @@
       </c>
       <c r="B7" s="20" t="inlineStr">
         <is>
-          <t>6 | 2112呎 (4+房)
+          <t>6 | 2169呎 (4+房)
 $19011万
-$90,014/呎
+$87,649/呎
 (22年-06月-02日)</t>
         </is>
       </c>
       <c r="C7" s="20" t="inlineStr">
         <is>
-          <t>7 | 2256呎 (4+房)
+          <t>7 | 2316呎 (4+房)
 $20389万
-$90,376/呎
+$88,035/呎
 (22年-06月-02日)</t>
         </is>
       </c>
@@ -9870,17 +9870,17 @@
       </c>
       <c r="B9" s="20" t="inlineStr">
         <is>
-          <t>6 | 2112呎 (4+房)
+          <t>6 | 2169呎 (4+房)
 $17200万
-$81,439/呎
+$79,299/呎
 (21年-11月-16日)</t>
         </is>
       </c>
       <c r="C9" s="20" t="inlineStr">
         <is>
-          <t>7 | 2256呎 (4+房)
+          <t>7 | 2316呎 (4+房)
 $19038万
-$84,388/呎
+$82,202/呎
 (21年-08月-16日)</t>
         </is>
       </c>
@@ -9893,17 +9893,17 @@
       </c>
       <c r="B10" s="20" t="inlineStr">
         <is>
-          <t>6 | 2112呎 (4+房)
+          <t>6 | 2169呎 (4+房)
 $16680万
-$78,977/呎
+$76,902/呎
 (22年-01月-31日)</t>
         </is>
       </c>
       <c r="C10" s="20" t="inlineStr">
         <is>
-          <t>7 | 2256呎 (4+房)
+          <t>7 | 2316呎 (4+房)
 $18523万
-$82,107/呎
+$79,980/呎
 (21年-10月-21日)</t>
         </is>
       </c>
@@ -9924,9 +9924,9 @@
       </c>
       <c r="C11" s="20" t="inlineStr">
         <is>
-          <t>7 | 2256呎 (4+房)
+          <t>7 | 2316呎 (4+房)
 $18000万
-$79,787/呎
+$77,720/呎
 (21年-10月-19日)</t>
         </is>
       </c>
@@ -9939,17 +9939,17 @@
       </c>
       <c r="B12" s="20" t="inlineStr">
         <is>
-          <t>6 | 2112呎 (4+房)
+          <t>6 | 2169呎 (4+房)
 $15930万
-$75,426/呎
+$73,444/呎
 (21年-10月-12日)</t>
         </is>
       </c>
       <c r="C12" s="20" t="inlineStr">
         <is>
-          <t>7 | 2256呎 (4+房)
+          <t>7 | 2316呎 (4+房)
 $17360万
-$76,950/呎
+$74,957/呎
 (21年-10月-19日)</t>
         </is>
       </c>
@@ -9962,17 +9962,17 @@
       </c>
       <c r="B13" s="20" t="inlineStr">
         <is>
-          <t>6 | 2112呎 (4+房)
+          <t>6 | 2169呎 (4+房)
 $15480万
-$73,295/呎
+$71,369/呎
 (21年-09月-10日)</t>
         </is>
       </c>
       <c r="C13" s="20" t="inlineStr">
         <is>
-          <t>7 | 2256呎 (4+房)
+          <t>7 | 2316呎 (4+房)
 $16800万
-$74,468/呎
+$72,539/呎
 (21年-04月-27日)</t>
         </is>
       </c>
@@ -9985,9 +9985,9 @@
       </c>
       <c r="B14" s="20" t="inlineStr">
         <is>
-          <t>6 | 2112呎 (4+房)
+          <t>6 | 2169呎 (4+房)
 $14000万
-$66,288/呎
+$64,546/呎
 (24年-05月-30日)</t>
         </is>
       </c>
@@ -10016,9 +10016,9 @@
       </c>
       <c r="C15" s="20" t="inlineStr">
         <is>
-          <t>7 | 2256呎 (4+房)
+          <t>7 | 2316呎 (4+房)
 $16280万
-$72,163/呎
+$70,294/呎
 (23年-04月-03日)</t>
         </is>
       </c>
@@ -10031,17 +10031,17 @@
       </c>
       <c r="B16" s="20" t="inlineStr">
         <is>
-          <t>6 | 2112呎 (4+房)
+          <t>6 | 2169呎 (4+房)
 $14400万
-$68,182/呎
+$66,390/呎
 (25年-09月-02日)</t>
         </is>
       </c>
       <c r="C16" s="20" t="inlineStr">
         <is>
-          <t>7 | 2256呎 (4+房)
+          <t>7 | 2316呎 (4+房)
 $15280万
-$67,730/呎
+$65,976/呎
 (23年-03月-21日)</t>
         </is>
       </c>
@@ -10054,9 +10054,9 @@
       </c>
       <c r="B17" s="20" t="inlineStr">
         <is>
-          <t>6 | 2112呎 (4+房)
+          <t>6 | 2169呎 (4+房)
 $13600万
-$64,394/呎
+$62,702/呎
 (23年-12月-12日)</t>
         </is>
       </c>
@@ -10085,9 +10085,9 @@
       </c>
       <c r="C18" s="20" t="inlineStr">
         <is>
-          <t>7 | 2256呎 (4+房)
+          <t>7 | 2316呎 (4+房)
 $14760万
-$65,426/呎
+$63,731/呎
 (26年-09月-01日)</t>
         </is>
       </c>
@@ -10100,17 +10100,17 @@
       </c>
       <c r="B19" s="20" t="inlineStr">
         <is>
-          <t>6 | 2112呎 (4+房)
+          <t>6 | 2169呎 (4+房)
 $13080万
-$61,932/呎
+$60,304/呎
 (26年-07月-06日)</t>
         </is>
       </c>
       <c r="C19" s="20" t="inlineStr">
         <is>
-          <t>7 | 2256呎 (4+房)
+          <t>7 | 2316呎 (4+房)
 $14420万
-$63,918/呎
+$62,263/呎
 (26年-07月-06日)</t>
         </is>
       </c>
@@ -10146,17 +10146,17 @@
       </c>
       <c r="B21" s="20" t="inlineStr">
         <is>
-          <t>6 | 2112呎 (4+房)
+          <t>6 | 2169呎 (4+房)
 $11700万
-$55,398/呎
+$53,942/呎
 (24年-07月-12日)</t>
         </is>
       </c>
       <c r="C21" s="20" t="inlineStr">
         <is>
-          <t>7 | 2256呎 (4+房)
+          <t>7 | 2316呎 (4+房)
 $13842万
-$61,357/呎
+$59,767/呎
 (26年-01月-26日)</t>
         </is>
       </c>
@@ -10169,9 +10169,9 @@
       </c>
       <c r="B22" s="20" t="inlineStr">
         <is>
-          <t>6 | 2112呎 (4+房)
+          <t>6 | 2169呎 (4+房)
 $11500万
-$54,451/呎
+$53,020/呎
 (24年-06月-12日)</t>
         </is>
       </c>
@@ -10215,17 +10215,17 @@
       </c>
       <c r="B24" s="20" t="inlineStr">
         <is>
-          <t>6 | 2032呎 (4+房)
+          <t>6 | 2089呎 (4+房)
 $12630万
-$62,156/呎
+$60,460/呎
 (25年-03月-14日)</t>
         </is>
       </c>
       <c r="C24" s="20" t="inlineStr">
         <is>
-          <t>7 | 2176呎 (4+房)
+          <t>7 | 2236呎 (4+房)
 $15430万
-$70,910/呎
+$69,007/呎
 (21年-10月-22日)</t>
         </is>
       </c>
